--- a/.planning/phases/136-read-surfaces-connections-panel-work-witnesses/136-NOVELTY-HARDCASES.xlsx
+++ b/.planning/phases/136-read-surfaces-connections-panel-work-witnesses/136-NOVELTY-HARDCASES.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Identity Spot-Check'!$A$1:$I$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Novelty Shades'!$A$1:$K$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Novelty Shades'!$A$1:$K$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4342,13 +4342,577 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr"/>
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>Cambridge University Library Ms. Add. 3356</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>990001398970205171</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, תהלים (w000112)</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>מחזור מנהג ארץ ישראל הקדמון.</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'מחזור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr"/>
+      <c r="C78" s="3" t="inlineStr"/>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Cambridge University Library Ms. T-S Misc. 33/03</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>990001413070205171</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, שמות (w000087)</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>מחזור מנהג אשכנז לשלש רגלים : ; קטעי גניזה.</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'מחזור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr"/>
+      <c r="C79" s="3" t="inlineStr"/>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II A 58</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>990001429050205171</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, ישעיהו (w000097)</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>מחזור מנהג ספרד לשלש רגלים.</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'מחזור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr"/>
+      <c r="C80" s="3" t="inlineStr"/>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II A 300/4</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>990001436770205171</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, דברים (w000090)</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>סדור מנהג קראים.</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr"/>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II A 810</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>990001442520205171</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, ויקרא (w000088)</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>סדור מנהג קראים (קטע).</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr"/>
+      <c r="C82" s="3" t="inlineStr"/>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II A 1006</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>990001444570205171</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, יחזקאל (w000099)</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>סדור מנהג קראים.</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr"/>
+      <c r="C83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II A 642</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>990001441300205171</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, במדבר (w000089)</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>סדור מנהג קראים (קטע).</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr"/>
+      <c r="C84" s="3" t="inlineStr"/>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Library of the Hungarian Academy of Sciences Ms. 116</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>990001035960205171</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>משנה תורה, ספר אהבה (w000176)</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>מחזור מנהג ספרד לראש השנה (קטע).</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'מחזור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr"/>
+      <c r="C85" s="3" t="inlineStr"/>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II A 834</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>990001442760205171</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, ירמיהו (w000098)</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>סדור מנהג קראים (קטעים).</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr"/>
+      <c r="C86" s="3" t="inlineStr"/>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II A 2007</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>990001454910205171</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, דניאל (w000120)</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>סדור מנהג קראים (קטעים).</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr"/>
+      <c r="C87" s="3" t="inlineStr"/>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II A 2060</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>990001455500205171</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, דברי הימים ב (w000124)</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>סדור מנהג קראים (קטעים).</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr"/>
+      <c r="C88" s="3" t="inlineStr"/>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II A 867</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>990001443150205171</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, דברי הימים א (w000123)</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>סדור מנהג קראים (קטעים).</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K76"/>
+  <autoFilter ref="A1:K88"/>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid verdict" error="Choose one of the listed shades, or 'unsure' / 'skip'. Free text is rejected." promptTitle="Shade verdict" prompt="Pick the shade that best fits, or 'unsure' / 'skip'. Blank = not yet answered." type="list">
-      <formula1>"confirms,refines_granularity,aid_more_specific,diverges_work,diverges_part,fills_gap,extends,alias_merge,unsure,skip"</formula1>
+    <dataValidation sqref="B2:B88" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid verdict" error="Choose one of the listed shades, or 'unsure' / 'skip'. Free text is rejected." promptTitle="Shade verdict" prompt="Pick the shade that best fits, or 'unsure' / 'skip'. Blank = not yet answered." type="list">
+      <formula1>"confirms,refines_granularity,aid_more_specific,diverges_work,diverges_part,container_predicts,fills_gap,extends,alias_merge,unsure,skip"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid correctness call" error="Choose 'catalogue_correct', 'claim_correct' or 'unclear', or leave blank." promptTitle="Correctness (divergence rows only)" prompt="Only answer if the Shade verdict is diverges_work or diverges_part. Otherwise leave blank." type="list">
+    <dataValidation sqref="C2:C88" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid correctness call" error="Choose 'catalogue_correct', 'claim_correct' or 'unclear', or leave blank." promptTitle="Correctness (divergence rows only)" prompt="Only answer if the Shade verdict is diverges_work or diverges_part. Otherwise leave blank." type="list">
       <formula1>"catalogue_correct,claim_correct,unclear"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4362,7 +4926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4372,14 +4936,14 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>This workbook is a labelling instrument for the novelty hard-case evaluation set (plan 136-03 Task 3). The Markdown file 136-NOVELTY-HARDCASES.md in the same phase directory remains the authoritative human-readable record of these 83 candidate cases and the reasoning for why each is hard; this workbook renders the SAME cases, in the SAME order, from one shared pre-numbered case list, split across two data sheets by the question type each case was actually built to support.</t>
+          <t>This workbook is a labelling instrument for the novelty hard-case evaluation set (plan 136-03 Task 3). The Markdown file 136-NOVELTY-HARDCASES.md in the same phase directory remains the authoritative human-readable record of these 95 candidate cases and the reasoning for why each is hard; this workbook renders the SAME cases, in the SAME order, from one shared pre-numbered case list, split across two data sheets by the question type each case was actually built to support.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>"Identity Spot-Check" (Classes 1-3): these rows compare two of OUR OWN claims to each other -- an A vs B "same underlying work?" judgment, no finding aid involved at all. "Novelty Shades" (Classes 4-6): these rows judge ONE claim against the finding aids -- the question genuinely varies here, which is why it carries the fuller shade vocabulary plus a Correctness column for divergence rows.</t>
+          <t>"Identity Spot-Check" (Classes 1-3): these rows compare two of OUR OWN claims to each other -- an A vs B "same underlying work?" judgment, no finding aid involved at all. "Novelty Shades" (Classes 4-7): these rows judge ONE claim against the finding aids -- the question genuinely varies here, which is why it carries the fuller shade vocabulary plus a Correctness column for divergence rows.</t>
         </is>
       </c>
     </row>
@@ -4525,146 +5089,146 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>fills_gap</t>
+          <t>container_predicts</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>the aids identify this fragment as nothing at all -- the genuine "previously unknown" case</t>
+          <t>an aid names a BROADER rite/cycle/ceremony/container -- a full standard-rite prayer-book (siddur/machzor) or a named ceremony/occasion -- whose STANDARD, PREDICTABLE content includes this specific unit, WITHOUT ever naming the unit itself (owner ruling H; e.g. the catalogue names 'מחזור מנהג אשכנז לשלש רגלים', the claim is a Yotzer for one of its festivals). Distinct from `confirms` (the aid never names this specific unit) and from `fills_gap` (the content IS predictable, so it is not 'previously unknown' -- under the pre-H enum this fell through to `fills_gap` by elimination). Excluded from the candidate toggle like every other non-`fills_gap` shade, but -- UNLIKE `diverges_work`/`diverges_part` -- shown NORMALLY, never hidden by default: there is no disagreement here to warn about, only a container relationship.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>extends</t>
+          <t>fills_gap</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>aids tie OTHER folios of the SAME manuscript to this work, but not this specific folio</t>
+          <t>the aids identify this fragment as nothing at all -- the genuine "previously unknown" case</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>alias_merge</t>
+          <t>extends</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>the two work_ids shown ARE the same underlying work, not yet canonically merged (Class 2's situation)</t>
+          <t>aids tie OTHER folios of the SAME manuscript to this work, but not this specific folio</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>unsure</t>
+          <t>alias_merge</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>you cannot judge this case from the information shown -- maps to `not_checked`, costs nothing, is a real and useful answer</t>
+          <t>the two work_ids shown ARE the same underlying work, not yet canonically merged (Class 2's situation)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>unsure</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>you cannot judge this case from the information shown -- maps to `not_checked`, costs nothing, is a real and useful answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>you choose not to judge this case at all -- recorded as skipped, NEVER filled from a draft `PROPOSAL`</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>`not_checked` (the fail-closed system default for an unrun/failed/abstained check) is not a verdict you pick directly -- `unsure` is its owner-facing equivalent.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Correctness (divergence rows only)</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Choose this when...</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>catalogue_correct</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>the catalogue/aid is right; our claim is the false positive -- owner ruling F: reading the real cases, this is the COMMON outcome</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>claim_correct</t>
+          <t>catalogue_correct</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>our claim is right; the aid is wrong, thinner, or itself mistaken</t>
+          <t>the catalogue/aid is right; our claim is the false positive -- owner ruling F: reading the real cases, this is the COMMON outcome</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>claim_correct</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>our claim is right; the aid is wrong, thinner, or itself mistaken</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
           <t>unclear</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>cannot tell which side is correct from the information shown</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Plausible answers (a reading aid -- any answer above is still valid)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Class 3 -- catalogue entry naming a different granularity of the same work (IDENTITY spot-check)</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>same_work, different_works</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Class 2 -- alias pairs (IDENTITY spot-check)</t>
+          <t>Class 3 -- catalogue entry naming a different granularity of the same work (IDENTITY spot-check)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4676,7 +5240,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Class 1 -- near-miss titles (IDENTITY spot-check)</t>
+          <t>Class 2 -- alias pairs (IDENTITY spot-check)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -4688,42 +5252,66 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 1 -- near-miss titles (IDENTITY spot-check)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>same_work, different_works</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
+          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>fills_gap, confirms, extends</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
           <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>container_predicts, fills_gap, confirms</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A5:B5"/>

--- a/.planning/phases/136-read-surfaces-connections-panel-work-witnesses/136-NOVELTY-HARDCASES.xlsx
+++ b/.planning/phases/136-read-surfaces-connections-panel-work-witnesses/136-NOVELTY-HARDCASES.xlsx
@@ -9,11 +9,15 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identity Spot-Check" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Novelty Shades" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vocabulary &amp; Instructions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heuristic-Demoted" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No-Source-Text" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vocabulary &amp; Instructions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Identity Spot-Check'!$A$1:$I$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Novelty Shades'!$A$1:$K$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Novelty Shades'!$A$1:$K$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Heuristic-Demoted'!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'No-Source-Text'!$A$1:$F$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -832,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -913,40 +917,44 @@
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Ms. B 3672</t>
+          <t>Ms. Evr. Antonin B 1104</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>990002098550205171</t>
+          <t>990000555880205171</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>כתר מלכות (רשב"ג/אבן גבירול) (w001129)</t>
+          <t>CLAIMED (this identification): תשובות האיי גאון (w000650) / CATALOGUE NAMES (found in the identification text): תשובות (w000543)</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>שאלות ותשובות מאת האי בן שרירא גאון (קטע).</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('תשובות') than the one this claim identifies ('תשובות האיי גאון'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling G -- see 136-GATE1-DECISIONS.md § G): plausibly `confirms`, NOT a divergence -- the catalogue's own free text ('שאלות ותשובות מאת האי בן שרירא גאון') already states this claim's identification; only the structured work-id keying differed (this class's own selector over-fired here) -- confirm or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -956,40 +964,44 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S Misc. 34.14</t>
+          <t>Allony, Nehemia Ms. 304</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>990051124400205171</t>
+          <t>990000413480205171</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>פירוש אבות לדוד הנגיד (w001135)</t>
+          <t>CLAIMED (this identification): משנה תורה, ספר זמנים (w000177) / CATALOGUE NAMES (found in the identification text): הגדה של פסח (w001159)</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>הגדה של פסח.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('הגדה של פסח') than the one this claim identifies ('משנה תורה, ספר זמנים'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -999,40 +1011,44 @@
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S Misc. 34.20</t>
+          <t>Ms. Evr. Antonin B 915</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>990051124460205171</t>
+          <t>990000555810205171</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>רס"ג, שמות תרגום (תפסיר תורה) (w000033)</t>
+          <t>CLAIMED (this identification): הלכות פסוקות (w001084) / CATALOGUE NAMES (found in the identification text): הלכות גדולות (w001196)</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>הלכות גדולות (בבא קמא).</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('הלכות גדולות') than the one this claim identifies ('הלכות פסוקות'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1042,40 +1058,44 @@
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S Misc. 34.23</t>
+          <t>Cambridge University Library Ms. Add. 3162</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>990051124490205171</t>
+          <t>990001398690205171</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>משנה תורה, ספר אהבה (w000176)</t>
+          <t>CLAIMED (this identification): משנה תורה, ספר אהבה (w000176) / CATALOGUE NAMES (found in the identification text): ברכת המזון (w001158)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>ברכת המזון.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ברכת המזון') than the one this claim identifies ('משנה תורה, ספר אהבה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1085,40 +1105,44 @@
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S Misc. 34.29</t>
+          <t>Cambridge University Library Ms. Add. 1246</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>990051124550205171</t>
+          <t>990001394270205171</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך, בראשית (w000086)</t>
+          <t>CLAIMED (this identification): ספר יוסיפון (ערבי) (w001152) / CATALOGUE NAMES (found in the identification text): יוסיפון (w000853)</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>יוסיפון בערבית.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('יוסיפון') than the one this claim identifies ('ספר יוסיפון (ערבי)'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling G -- see 136-GATE1-DECISIONS.md § G): plausibly `confirms`, NOT a divergence -- the catalogue's own free text ('יוסיפון בערבית') already states this claim's identification; only the structured work-id keying differed (this class's own selector over-fired here) -- confirm or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1128,40 +1152,44 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.5</t>
+          <t>Ms. Evr. Antonin B 961</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>990051220230205171</t>
+          <t>990000555730205171</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>נתנאל בן פיומי, גן השכלים (w000039)</t>
+          <t>CLAIMED (this identification): תשובה בעניין סוכה (w000434) / CATALOGUE NAMES (found in the identification text): תשובות הגאונים (w000349)</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>שאלות ותשובות הגאונים.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('תשובות הגאונים') than the one this claim identifies ('תשובה בעניין סוכה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1171,40 +1199,44 @@
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.26</t>
+          <t>Ms. EVR ARAB I 3085</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>990051220440205171</t>
+          <t>990000801470205171</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>הלכות גדולות (w001196)</t>
+          <t>CLAIMED (this identification): רס"ג, ספר יצירה פירוש (w000021) / CATALOGUE NAMES (found in the identification text): ספר יצירה (w000522)</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>פרוש ספר יצירה בערבית.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ספר יצירה') than the one this claim identifies ('רס"ג, ספר יצירה פירוש'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1214,40 +1246,44 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.28</t>
+          <t>Catalogue Halper, Philadelphia 120</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>990051220460205171</t>
+          <t>990001935160205171</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>מדרש אגור (w000836)</t>
+          <t>CLAIMED (this identification): הלכות פסוקות, תרגומים ועיבודים עבריים, הלכות קידושין (w001037) / CATALOGUE NAMES (found in the identification text): הלכות פסוקות (w001084)</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>הלכות פסוקות (קדושין).</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('הלכות פסוקות') than the one this claim identifies ('הלכות פסוקות, תרגומים ועיבודים עבריים, הלכות קידושין'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_part` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1257,40 +1293,44 @@
       <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.34</t>
+          <t>Ms. Evr. Antonin B 236</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>990051220530205171</t>
+          <t>990000905560205171</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>תשובות האיי גאון (w000654)</t>
+          <t>CLAIMED (this identification): מכילתא דרבי שמעון בן יוחאי (w000321) / CATALOGUE NAMES (found in the identification text): מכילתא דרבי ישמעאל (w000766)</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>מכילתא דרבי ישמעאל (בא-יתרו).</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('מכילתא דרבי ישמעאל') than the one this claim identifies ('מכילתא דרבי שמעון בן יוחאי'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1300,40 +1340,44 @@
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.35</t>
+          <t>Library of the Hungarian Academy of Sciences Ms. 57</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>990051220540205171</t>
+          <t>990001004230205171</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>מונחי המסורה וכלליה (w000906)</t>
+          <t>CLAIMED (this identification): ילקוט שמעוני על התורה (w001384) / CATALOGUE NAMES (found in the identification text): תנחומא (w000926)</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>מדרש תנחומא (קטעים).</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('תנחומא') than the one this claim identifies ('ילקוט שמעוני על התורה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1343,40 +1387,44 @@
       <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.39</t>
+          <t>Cambridge University Library Ms. T-S NS 169.52</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>990051220580205171</t>
+          <t>990051091870205171</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>סדר אליהו זוטא א-טו (w000162)</t>
+          <t>CLAIMED (this identification): נסים גאון, חמשה ספרים (w000071) / CATALOGUE NAMES (found in the identification text): מגילת סתרים (w000509)</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>הלכה; מגילת סתרים [נסים בן יעקב]; ספרות הלכתית ופרשנות תלמודית; ספרות חז"ל. ; Halakhic Literature and Talmudic Commentaries ; Rabbinica; exposition of PT hagigah 78a and Tosefta Sheqalim 3:23-24 (the latter section numbered 140).</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('מגילת סתרים') than the one this claim identifies ('נסים גאון, חמשה ספרים'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1386,40 +1434,44 @@
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.41</t>
+          <t>Cambridge University Library Ms. T-S F 7.45</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>990051220600205171</t>
+          <t>990051173260205171</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך, ויקרא (w000088)</t>
+          <t>CLAIMED (this identification): משנה תורה, הקדמה ומניין המצוות (w000174) / CATALOGUE NAMES (found in the identification text): הלכות ציצית (w001052)</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>משנה תורה;משנה תורה ופירושיו. ; Mishneh Torah and its Commentaries ; מנין מצות על סדר הרמב"ם, מסוף ספר אהבה (הלכות ציצית) עד סוף ספר זמנים</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('הלכות ציצית') than the one this claim identifies ('משנה תורה, הקדמה ומניין המצוות'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_part` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1429,40 +1481,44 @@
       <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.42</t>
+          <t>Ms. EVR II A 33</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>990051220610205171</t>
+          <t>990000621960205171</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>דברי הימים של משה רבנו (w000944)</t>
+          <t>CLAIMED (this identification): תנ"ך, בראשית (w000086) / CATALOGUE NAMES (found in the identification text): שאילתות (w000732)</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>שאילתות.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('שאילתות') than the one this claim identifies ('תנ"ך, בראשית'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1472,40 +1528,44 @@
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.46</t>
+          <t>Cambridge University Library Ms. T-S C 1.23</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>990051220650205171</t>
+          <t>990051150540205171</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>פירוש ליחזקאל ותרי עשר (w000918)</t>
+          <t>CLAIMED (this identification): בראשית רבה צה-צו, תוספת (w000900) / CATALOGUE NAMES (found in the identification text): בראשית רבה (w000156)</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>בראשית רבה;מדרש. ; Midrash ; בראשית רבה</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('בראשית רבה') than the one this claim identifies ('בראשית רבה צה-צו, תוספת'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_part` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1515,40 +1575,44 @@
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.48</t>
+          <t>Cambridge University Library Ms. T-S Misc. 15.67</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>990051220670205171</t>
+          <t>990051080280205171</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>מדרש חסרות ויתרות (w000859)</t>
+          <t>CLAIMED (this identification): ויקרא רבה (w000169) / CATALOGUE NAMES (found in the identification text): חובות הלבבות (תרגום אבן תיבון) (w000195)</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>חובות הלבבות (תרגום אבן תיבון). ; ספר חובות הלבבות. מעלת התשובה ומעלת הצדקה. דפוס.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('חובות הלבבות (תרגום אבן תיבון)') than the one this claim identifies ('ויקרא רבה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1558,40 +1622,44 @@
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.53</t>
+          <t>Library of the Alliance Israélite Un Ms. III A 101</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>990051220720205171</t>
+          <t>990001506030205171</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>מחברת (w000911)</t>
+          <t>CLAIMED (this identification): רי"ף ברכות (w001317) / CATALOGUE NAMES (found in the identification text): מסכת דרך ארץ זוטא (w000787)</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>מסכת דרך ארץ זוטא (פרק השלום).</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('מסכת דרך ארץ זוטא') than the one this claim identifies ('רי"ף ברכות'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1601,40 +1669,44 @@
       <c r="C18" s="3" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.56</t>
+          <t>Cambridge University Library Ms. T-S C 1.19</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>990051220750205171</t>
+          <t>990051150500205171</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>הלכות פסוקות (w001084)</t>
+          <t>CLAIMED (this identification): פסיקתא דרב כהנא (w000904) / CATALOGUE NAMES (found in the identification text): ויקרא רבה (w000169)</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>ויקרא רבה;מדרש. ; Midrash ; ויקרא רבה</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ויקרא רבה') than the one this claim identifies ('פסיקתא דרב כהנא'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1644,40 +1716,44 @@
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S K 27.33b</t>
+          <t>Cambridge University Library Ms. T-S NS 291.103</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>990051221550205171</t>
+          <t>990051104680205171</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך, דברים (w000090)</t>
+          <t>CLAIMED (this identification): רד"ק על יחזקאל (w001245) / CATALOGUE NAMES (found in the identification text): מדרש תהלים (w001124)</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>מדרש תהלים; ספרות הלכתית ופרשנות תלמודית; ספרות חז"ל; פירוש רד"ק למקרא. ; דוד בן יוסף קמחי, פירוש רד"ק למקרא: יחזקאל ח:א – יא</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('מדרש תהלים') than the one this claim identifies ('רד"ק על יחזקאל'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1687,40 +1763,44 @@
       <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S 8 K 3</t>
+          <t>Adler, Elkan Nathan Ms. 2160.12</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>990051232460205171</t>
+          <t>990053147670205171</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>חיבור נגד אל-קומסי (w001057)</t>
+          <t>CLAIMED (this identification): רס"ג, איכה תרגום (w000012) / CATALOGUE NAMES (found in the identification text): תרגום איכה (w001413)</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>מקרא [טקסט];תפסיר ערבי. ; תרגום איכה ד:א-כא לערבית-יהודית</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('תרגום איכה') than the one this claim identifies ('רס"ג, איכה תרגום'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1730,40 +1810,44 @@
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S 8 K 13.8</t>
+          <t>Ms. EVR ARAB I 1771</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>990051232630205171</t>
+          <t>990001535860205171</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>תשובות הרמב״ם ב (w001143)</t>
+          <t>CLAIMED (this identification): ראב"ש, שמואל א פירוש (w000046) / CATALOGUE NAMES (found in the identification text): ספר הרקמה (w000037)</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>_(none on file -- explicit marker of absence, not an omission)_</t>
+          <t>כתאב אלאסל : ; ספר הרקמה בערבית.</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification field is EMPTY -- there is no catalogue text at all for a title comparison to work with, only the identified work's title itself.</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ספר הרקמה') than the one this claim identifies ('ראב"ש, שמואל א פירוש'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1773,42 +1857,42 @@
       <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S G 2.23</t>
+          <t>Cambridge University Library Ms. T-S E 1.2</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>990051181330205171</t>
+          <t>990051158320205171</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>תשובות האיי גאון (w000695) -- one of 43 works sharing author 'האיי גאון' and title stem 'תשובות האיי גאון' (siblings incl. w000650, w000651, w000652, w000653, w000654...)</t>
+          <t>CLAIMED (this identification): משנה, פאה (w000259) / CATALOGUE NAMES (found in the identification text): ברייתא דמלאכת המשכן (w000157)</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות- גאונים. ; Responsa- Gaonim</t>
+          <t>ברייתא דמלאכת המשכן;מסכת גרים;משנה [טקסט]. ; Mishnah: Pe'ah 4:4 – 6:3; Berakhot 1:1 – 3:1 ; משנה: פאה ד:ד – ו:ג; ברכות א:א – ג:א</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 43-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ברייתא דמלאכת המשכן') than the one this claim identifies ('משנה, פאה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
         </is>
       </c>
     </row>
@@ -1820,42 +1904,42 @@
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S G 2.29</t>
+          <t>Cambridge University Library Ms. T-S C 6.113</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>990051181390205171</t>
+          <t>990051154860205171</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>תשובות שרירא גאון והאיי גאון (w000629) -- one of 33 works sharing author 'שרירא גאון והאיי גאון' and title stem 'תשובות שרירא גאון והאיי גאון' (siblings incl. w000597, w000599, w000600, w000601, w000602...)</t>
+          <t>CLAIMED (this identification): תלמוד בבלי, מגילה (w000957) / CATALOGUE NAMES (found in the identification text): ספרי דברים (w000166)</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות- גאונים. ; Responsa- Gaonim</t>
+          <t>ספרי דברים;פירוש אבן עזרא למקרא;פרשנות מקרא. ; Sifre on Deuteronomy: 11:399 – 15:400; 7:404 – 15:400[בדילוגים] ; ספרי דברים: יא:399 – טו:400; ז:404 – טו:400[בדילוגים]</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 33-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ספרי דברים') than the one this claim identifies ('תלמוד בבלי, מגילה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
         </is>
       </c>
     </row>
@@ -1867,42 +1951,42 @@
       <c r="C24" s="3" t="inlineStr"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. L-G Talm. II 1</t>
+          <t>Cambridge University Library Ms. T-S F 17.48</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>990001843080205171</t>
+          <t>990051180030205171</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>תשובות צמח גאון (w000573) -- one of 12 works sharing author 'צמח גאון' and title stem 'תשובות צמח גאון' (siblings incl. w000562, w000563, w000564, w000565, w000566...)</t>
+          <t>CLAIMED (this identification): ויקרא רבה (w000169) / CATALOGUE NAMES (found in the identification text): קהלת רבה (w000891)</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>תשובות הגאונים.</t>
+          <t>קהלת רבה;תלמוד ירושלמי [טקסט]. ; Midrash Rabbah Ecclesiastes: 5 ; קהלת רבה: ה</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 12-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('קהלת רבה') than the one this claim identifies ('ויקרא רבה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
         </is>
       </c>
     </row>
@@ -1914,42 +1998,42 @@
       <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S NS 309.106</t>
+          <t>Cambridge University Library Ms. T-S F 2(2).64</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>990051703120205171</t>
+          <t>990051167990205171</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>תשובות שרירא גאון (w000581) -- one of 9 works sharing author 'שרירא גאון' and title stem 'תשובות שרירא גאון' (siblings incl. w000582, w000584, w000589, w000590, w000591...)</t>
+          <t>CLAIMED (this identification): תלמוד בבלי, עבודה זרה (w000973) / CATALOGUE NAMES (found in the identification text): פסיקתא דרב כהנא (w000904)</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>ספרות הלכתית ופרשנות תלמודית;ספרות חז"ל;שאלות ותשובות- גאונים. ; Halakhic Literature and Talmudic Commentaries ; Responsa; geonic, concerning oaths (whether a married woman should be made to swear in court, and whether some members of a partnership can waive an oath due them without the remaining partners consent).</t>
+          <t>מדרש;פסיקתא דרב כהנא;תלמוד בבלי [טקסט]. ; Talmud Bavli: Niddah 31 a – b; Sotah 44 b – 45 b; Avodah Zarah 51 a – 52 b ; תלמוד בבלי: נידה לא ע"א – ע"ב; סוטה מד ע"ב – מה ע"ב; עבודה זרה נא ע"א – נב ע"ב</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 9-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('פסיקתא דרב כהנא') than the one this claim identifies ('תלמוד בבלי, עבודה זרה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
         </is>
       </c>
     </row>
@@ -1961,42 +2045,42 @@
       <c r="C26" s="3" t="inlineStr"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Catalogue Brumer Rab. 2360, fol. 1</t>
+          <t>Cambridge University Library Ms. L-G Talm. I 45</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>990053344530205171</t>
+          <t>990001842460205171</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>תשובות שמואל גאון (w000428) -- one of 6 works sharing author 'שמואל גאון' and title stem 'תשובות שמואל גאון' (siblings incl. w000429, w000430, w000432, w000433, w000435)</t>
+          <t>CLAIMED (this identification): הלכות ארץ ישראליות ובבליות וליקוטים ממעשים לבני ארץ ישראל (w001075) / CATALOGUE NAMES (found in the identification text): מעשים לבני ארץ ישראל (w001030)</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות- גאונים. ; תשובות בעניין המגרש בגט בטל, אונאה וחזרה במכירת קרקע</t>
+          <t>מעשים לבני ארץ ישראל.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 6-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('מעשים לבני ארץ ישראל') than the one this claim identifies ('הלכות ארץ ישראליות ובבליות וליקוטים ממעשים לבני ארץ ישראל'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
         </is>
       </c>
     </row>
@@ -2008,42 +2092,42 @@
       <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Ms. Evr. Antonin B 266</t>
+          <t>MS heb. e.22/1</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>990000907150205171</t>
+          <t>990053426460205171</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>תשובות יצחק (w000559) -- one of 5 works sharing author 'נחשון גאון' and title stem 'תשובות יצחק' (siblings incl. w000554, w000556, w000557, w000561)</t>
+          <t>CLAIMED (this identification): הלכות פסוקות (w001084) / CATALOGUE NAMES (found in the identification text): והזהיר (w000779)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות הגאונים.</t>
+          <t>ספר והזהיר. ; והזהיר, פסק"ז</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 5-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('והזהיר') than the one this claim identifies ('הלכות פסוקות'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
         </is>
       </c>
     </row>
@@ -2055,42 +2139,42 @@
       <c r="C28" s="3" t="inlineStr"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S G 1.78</t>
+          <t>Cambridge University Library Ms. T-S NS 309.81</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>990051180910205171</t>
+          <t>990051106940205171</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>תשובות נטרונאי גאון (w000534) -- one of 5 works sharing author 'נטרונאי גאון' and title stem 'תשובות נטרונאי גאון' (siblings incl. w000535, w000536, w000537, w000538)</t>
+          <t>CLAIMED (this identification): מסכת דרך ארץ זוטא (w000787) / CATALOGUE NAMES (found in the identification text): מסכת דרך ארץ רבה (w000786)</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות. ; Responsa and Halakhic Decisions</t>
+          <t>מסכת דרך ארץ רבה; סידור שלמה מסיג'ילמאסה; ספרות הלכתית ופרשנות תלמודית; ספרות חז"ל; קולופון. ; Halakhic Literature and Talmudic Commentaries ; שלמה בן נתן מסיג'ילמאסה, סידור שלמה מסיג'ילמאסה: ל</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 5-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('מסכת דרך ארץ רבה') than the one this claim identifies ('מסכת דרך ארץ זוטא'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
         </is>
       </c>
     </row>
@@ -2102,38 +2186,42 @@
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S 20.183</t>
+          <t>Adler, Elkan Nathan Ms. 2700.24</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>990051346380205171</t>
+          <t>990053586310205171</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>תשובות עמרם גאון (w000553) -- one of 5 works sharing author 'עמרם גאון' and title stem 'תשובות עמרם גאון' (siblings incl. w000547, w000548, w000551, w000552)</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr"/>
+          <t>CLAIMED (this identification): פירוש המשנה, נזיקין (w000028) / CATALOGUE NAMES (found in the identification text): משנה, סנהדרין (w000291)</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>משנה [טקסט];פירוש המשנה לרמב"ם [ערבית]. ; פירוש הרמב"ם למשנה, סנהדרין י:א, ההקדמה לפרק חלק, עיקרים ראשון ושני (מהד' קאפח ע' רי-ריא).</t>
+        </is>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 5-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('משנה, סנהדרין') than the one this claim identifies ('פירוש המשנה, נזיקין'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
         </is>
       </c>
     </row>
@@ -2145,42 +2233,42 @@
       <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S G 2.14</t>
+          <t>Cambridge University Library Ms. T-S C 1.60</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>990051181240205171</t>
+          <t>990051150910205171</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>תשובות פלטוי גאון (w000542) -- one of 4 works sharing author 'פלטוי גאון' and title stem 'תשובות פלטוי גאון' (siblings incl. w000539, w000540, w000541)</t>
+          <t>CLAIMED (this identification): ברייתא דישועה, הפירוש, נוסח אחר (w000755) / CATALOGUE NAMES (found in the identification text): ברייתא דישועה (w000754)</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות- גאונים. ; Responsa- Gaonim</t>
+          <t>ברייתא דישועה;מדרש. ; Midrash ; ברייתא דישועה</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 4-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ברייתא דישועה') than the one this claim identifies ('ברייתא דישועה, הפירוש, נוסח אחר'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
         </is>
       </c>
     </row>
@@ -2192,42 +2280,42 @@
       <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Ms. Evr. Antonin B 308</t>
+          <t>Cambridge University Library Ms. T-S NS 329/0609</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>990000555750205171</t>
+          <t>990001420410205171</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>תשובות שר שלום גאון (w000499) -- one of 4 works sharing author 'שר שלום גאון' and title stem 'תשובות שר שלום גאון' (siblings incl. w000497, w000498, w000500)</t>
+          <t>CLAIMED (this identification): פסיקתא, ״אנכי אדוני אלהיך״ (איש שלום צח) (w000506) / CATALOGUE NAMES (found in the identification text): פסיקתא רבתי (w000803)</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות הגאונים.</t>
+          <t>פסיקתא רבתי (פרשה כג:ו) :</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 4-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('פסיקתא רבתי') than the one this claim identifies ('פסיקתא, ״אנכי אדוני אלהיך״ (איש שלום צח)'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
         </is>
       </c>
     </row>
@@ -2239,42 +2327,42 @@
       <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S 8 G 7.2</t>
+          <t>Ms. Evr. Antonin B 3</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>990051222370205171</t>
+          <t>990000905190205171</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>תשובות יוסף בן אביתור (w000730) -- one of 3 works sharing author 'יוסף בן אביתור' and title stem 'תשובות יוסף בן אביתור' (siblings incl. w000729, w000731)</t>
+          <t>משנה, אבות (w000296)</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות- גאונים.</t>
+          <t>סדור מנהג רומניא לכל השנה (קטע). משנה [טקסט] Mishnah [Text] משנה [טקסט] Mishnah [Text] משנה [טקסט] Mishnah [Text]</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 3-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `container_predicts`: this manuscript's own catalogue text names a specific, NAMED standard-rite container (a container noun immediately followed by מנהג) whose standard, predictable content plausibly includes this claimed unit, without the catalogue ever naming the unit itself -- folds in the former Class 7 (owner rulings H/I). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `container_predicts` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2286,42 +2374,42 @@
       <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S G 1.86</t>
+          <t>Ms. Evr. Antonin B 3</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>990051180990205171</t>
+          <t>990000905190205171</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>תשובות משרשיה (w000528) -- one of 3 works sharing author 'משה (משרשיה) הכהן גאון' and title stem 'תשובות משרשיה' (siblings incl. w000527, w000529)</t>
+          <t>הלכות מסידור (w000345)</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות;שאלות ותשובות- גאונים. ; Responsa and Halakhic Decisions ; ד' תשובות בענייני כתובה: א. כנראה בעניין אשה שהוציאה שטר כתובה ונמצא מזוייף. ב. תשובת רב צמח גאון בעניין אשה שאבדה כתובתה. ג. תשובת רב צמח גאון בעניין פירוש דברי רב רב יוסף "בביתי ולא בביקתי" (כתובות נד ע"א). ד. תשובת מר רבנא משה גאון (בן יעקב, ראש ישיבת מתא מחסיא) בעניין בחור שנשא אשה והתברר שהיא נכפית.</t>
+          <t>סדור מנהג רומניא לכל השנה (קטע). משנה [טקסט] Mishnah [Text] משנה [טקסט] Mishnah [Text] משנה [טקסט] Mishnah [Text]</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 3-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `container_predicts`: this manuscript's own catalogue text names a specific, NAMED standard-rite container (a container noun immediately followed by מנהג) whose standard, predictable content plausibly includes this claimed unit, without the catalogue ever naming the unit itself -- folds in the former Class 7 (owner rulings H/I). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `container_predicts` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2333,42 +2421,42 @@
       <c r="C34" s="3" t="inlineStr"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Ms. EVR II A 721</t>
+          <t>Library of the Hungarian Academy of Sciences Ms. 116</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>990001442050205171</t>
+          <t>990001035960205171</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>תשובות קלונימוס הזקן מלוקא בר׳ משה (w000416) -- one of 3 works sharing author 'קלונימוס הזקן מלוקא בר׳ משה' and title stem 'תשובות קלונימוס הזקן מלוקא בר משה' (siblings incl. w000760, w000761)</t>
+          <t>התגלות הסודות (w000052)</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>תשובות.</t>
+          <t>מחזור מנהג ספרד לראש השנה (קטע).</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 3-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `container_predicts`: this manuscript's own catalogue text names a specific, NAMED standard-rite container (a container noun immediately followed by מנהג) whose standard, predictable content plausibly includes this claimed unit, without the catalogue ever naming the unit itself -- folds in the former Class 7 (owner rulings H/I). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `container_predicts` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2380,42 +2468,42 @@
       <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S 16.99</t>
+          <t>Library of the Hungarian Academy of Sciences Ms. 116</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>990051341890205171</t>
+          <t>990001035960205171</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>תשובות האיי גאון (w000694) -- one of 43 works sharing author 'האיי גאון' and title stem 'תשובות האיי גאון' (siblings incl. w000650, w000651, w000652, w000653, w000654...)</t>
+          <t>תנ"ך, ישעיהו (w000097)</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות;שאלות ותשובות- גאונים. ; Responsa- Gaonim ; שאלות ותשובות- גאונים</t>
+          <t>מחזור מנהג ספרד לראש השנה (קטע).</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 43-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `container_predicts`: this manuscript's own catalogue text names a specific, NAMED standard-rite container (a container noun immediately followed by מנהג) whose standard, predictable content plausibly includes this claimed unit, without the catalogue ever naming the unit itself -- folds in the former Class 7 (owner rulings H/I). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `container_predicts` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2427,42 +2515,42 @@
       <c r="C36" s="3" t="inlineStr"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Ms. EVR II A 32</t>
+          <t>Library of the Hungarian Academy of Sciences Ms. 116</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>990001428310205171</t>
+          <t>990001035960205171</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>תשובות שרירא גאון והאיי גאון (w000606) -- one of 33 works sharing author 'שרירא גאון והאיי גאון' and title stem 'תשובות שרירא גאון והאיי גאון' (siblings incl. w000597, w000599, w000600, w000601, w000602...)</t>
+          <t>משנה תורה, ספר אהבה (w000176)</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות הגאונים.</t>
+          <t>מחזור מנהג ספרד לראש השנה (קטע).</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 33-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `container_predicts`: this manuscript's own catalogue text names a specific, NAMED standard-rite container (a container noun immediately followed by מנהג) whose standard, predictable content plausibly includes this claimed unit, without the catalogue ever naming the unit itself -- folds in the former Class 7 (owner rulings H/I). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `container_predicts` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2474,42 +2562,42 @@
       <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S Loan Collection 98</t>
+          <t>Ms. 2069</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>990051125820205171</t>
+          <t>990000617200205171</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>תשובות צמח גאון (w000570) -- one of 12 works sharing author 'צמח גאון' and title stem 'תשובות צמח גאון' (siblings incl. w000562, w000563, w000564, w000565, w000566...)</t>
+          <t>כתר מלכות (רשב"ג/אבן גבירול) (w001129)</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות- גאונים. ; Lists, Responsa lists ; רשימות, רשימות שו"ת</t>
+          <t>תפלות על דרך הקבלה.</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 12-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `terse_catalogue`: this manuscript's own catalogue identification field is empty or too short (&lt;=20 characters) to compare against -- folds in the former Class 4 (terse/missing catalogue text). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2521,42 +2609,42 @@
       <c r="C38" s="3" t="inlineStr"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S 12.459</t>
+          <t>Ms. EVR II A 28</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>990051337150205171</t>
+          <t>990000621930205171</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>תשובות שרירא גאון (w000581) -- one of 9 works sharing author 'שרירא גאון' and title stem 'תשובות שרירא גאון' (siblings incl. w000582, w000584, w000589, w000590, w000591...)</t>
+          <t>נסים גאון, חמשה ספרים (w000071)</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>תשובות הגאונים (קטע).</t>
+          <t>קובץ ברפואה.</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 9-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `terse_catalogue`: this manuscript's own catalogue identification field is empty or too short (&lt;=20 characters) to compare against -- folds in the former Class 4 (terse/missing catalogue text). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2568,42 +2656,42 @@
       <c r="C39" s="3" t="inlineStr"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Ms. Evr. Antonin B 1037</t>
+          <t>Ms. EVR II A 28</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>990000555740205171</t>
+          <t>990000621930205171</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>תשובות שמואל גאון (w000428) -- one of 6 works sharing author 'שמואל גאון' and title stem 'תשובות שמואל גאון' (siblings incl. w000429, w000430, w000432, w000433, w000435)</t>
+          <t>היכלות רבתי (w000170)</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות הגאונים.</t>
+          <t>קובץ ברפואה.</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 6-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `terse_catalogue`: this manuscript's own catalogue identification field is empty or too short (&lt;=20 characters) to compare against -- folds in the former Class 4 (terse/missing catalogue text). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2615,42 +2703,42 @@
       <c r="C40" s="3" t="inlineStr"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>MS heb. c.23/43</t>
+          <t>Ms. EVR II A 28</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>990053397750205171</t>
+          <t>990000621930205171</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>תשובות יצחק (w000559) -- one of 5 works sharing author 'נחשון גאון' and title stem 'תשובות יצחק' (siblings incl. w000554, w000556, w000557, w000561)</t>
+          <t>ספר יצירה (w000522)</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות. ; תשובות</t>
+          <t>קובץ ברפואה.</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 5-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `terse_catalogue`: this manuscript's own catalogue identification field is empty or too short (&lt;=20 characters) to compare against -- folds in the former Class 4 (terse/missing catalogue text). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2662,42 +2750,42 @@
       <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S G 1.87</t>
+          <t>Ms. EVR II A 28</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>990051181000205171</t>
+          <t>990000621930205171</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>תשובות נטרונאי גאון (w000534) -- one of 5 works sharing author 'נטרונאי גאון' and title stem 'תשובות נטרונאי גאון' (siblings incl. w000535, w000536, w000537, w000538)</t>
+          <t>מסכת היכלות (w000840)</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות;שאלות ותשובות- גאונים. ; Responsa and Halakhic Decisions ; ו' תשובות רב נטרונאי גאון: א. בעניין קבורת מת ביום טוב שני של גלויות. ב. בעניין הכרעת ההלכה בסוגיית "כשותא בכרמא" (שבת קלט ע"א). ג. בעניין הכרעת ההלכה בסוגיית "אין מוליכין חלה ומתנות לכהן ביום טוב" (ביצה דף יב ע"ב). ד. אם נוהגת תרומה בזמן הזה. ה. פירוש דברי הגמרא "ומסיקין ואופין בפורני" (ביצה לד ע"א). ו. בעניין אפיה ביום טוב בתנור של גוי.</t>
+          <t>קובץ ברפואה.</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 5-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `terse_catalogue`: this manuscript's own catalogue identification field is empty or too short (&lt;=20 characters) to compare against -- folds in the former Class 4 (terse/missing catalogue text). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2709,42 +2797,42 @@
       <c r="C42" s="3" t="inlineStr"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>MS heb. d.63/70</t>
+          <t>Ms. EVR II A 6</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>990053419080205171</t>
+          <t>990000589160205171</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>תשובות עמרם גאון (w000547) -- one of 5 works sharing author 'עמרם גאון' and title stem 'תשובות עמרם גאון' (siblings incl. w000548, w000551, w000552, w000553)</t>
+          <t>נסים גאון, חמשה ספרים (w000071)</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות;שאלות ותשובות- גאונים. ; פירושים לתלמוד בתשובות גאונים, בהלכות ציצית ע"פ מנחות ועוד לט-מג; ר' נטרונאי גאון?</t>
+          <t>קובץ. זוהר</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 5-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `bib_sole`: the Friedberg bibliography has text for this manuscript that does NOT name this specific claimed work (no other checked source has any text at all for this manuscript). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2756,38 +2844,42 @@
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S 12.854</t>
+          <t>Ms. EVR II A 6</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>990051340950205171</t>
+          <t>990000589160205171</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>תשובות פלטוי גאון (w000541) -- one of 4 works sharing author 'פלטוי גאון' and title stem 'תשובות פלטוי גאון' (siblings incl. w000539, w000540, w000542)</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr"/>
+          <t>היכלות רבתי (w000170)</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>קובץ. זוהר</t>
+        </is>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 4-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `bib_sole`: the Friedberg bibliography has text for this manuscript that does NOT name this specific claimed work (no other checked source has any text at all for this manuscript). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2799,42 +2891,42 @@
       <c r="C44" s="3" t="inlineStr"/>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>MS heb. c.18/40</t>
+          <t>Ms. EVR II A 6</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>990053395550205171</t>
+          <t>990000589160205171</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>תשובות שר שלום גאון (w000498) -- one of 4 works sharing author 'שר שלום גאון' and title stem 'תשובות שר שלום גאון' (siblings incl. w000497, w000499, w000500)</t>
+          <t>ספר יצירה (w000522)</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות- גאונים. ; תשובות הגאונים, ברכות ה,א\ פסחים עד,ב</t>
+          <t>קובץ. זוהר</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 4-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `bib_sole`: the Friedberg bibliography has text for this manuscript that does NOT name this specific claimed work (no other checked source has any text at all for this manuscript). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2846,42 +2938,42 @@
       <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Adler, Elkan Nathan Ms. 2632.1</t>
+          <t>Ms. EVR II A 6</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>990053180470205171</t>
+          <t>990000589160205171</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>תשובות יוסף בן אביתור (w000730) -- one of 3 works sharing author 'יוסף בן אביתור' and title stem 'תשובות יוסף בן אביתור' (siblings incl. w000729, w000731)</t>
+          <t>מדרש עשרת הרוגי מלכות, נוסח ארוך (w000937)</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות;שאלות ותשובות- גאונים. ; תשובות שונות לגאון או לר' יוסף אבן אביתור?</t>
+          <t>קובץ. זוהר</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 3-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `bib_sole`: the Friedberg bibliography has text for this manuscript that does NOT name this specific claimed work (no other checked source has any text at all for this manuscript). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2893,42 +2985,42 @@
       <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Ms. EVR II A 32</t>
+          <t>Ms. EVR II A 6</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>990001428310205171</t>
+          <t>990000589160205171</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>תשובות האיי גאון (w000670) -- one of 43 works sharing author 'האיי גאון' and title stem 'תשובות האיי גאון' (siblings incl. w000650, w000651, w000652, w000653, w000654...)</t>
+          <t>רד"ק על דברי הימים א׳ (w001249)</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות הגאונים.</t>
+          <t>קובץ. זוהר</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>This work belongs to a 43-member same-author/same-title-stem collection (a generic responsa/piyyut/collection title recurring across many distinct catalogued items) with &gt;=2 distinct canonical_work_ids in the cluster -- whether THIS witness is 'already recorded' is genuinely ill-defined at the collection level, not merely hard for a string comparison to settle.</t>
+          <t>Residual stratum `bib_sole`: the Friedberg bibliography has text for this manuscript that does NOT name this specific claimed work (no other checked source has any text at all for this manuscript). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): a generic collection member -- confirm whether this specific witness/passage is already recorded, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2940,42 +3032,42 @@
       <c r="C47" s="3" t="inlineStr"/>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Ms. Evr. Antonin B 1104</t>
+          <t>Ms. EVR ARAB I 1722</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>990000555880205171</t>
+          <t>990001535460205171</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): תשובות האיי גאון (w000650) / CATALOGUE NAMES (found in the identification text): תשובות (w000543)</t>
+          <t>פירוש המשנה, נשים (w000024)</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות מאת האי בן שרירא גאון (קטע).</t>
+          <t>ספר תשובה. כתאב אלרד</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('תשובות') than the one this claim identifies ('תשובות האיי גאון'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `fgp_sole`: an FGP transcription's own title/author fields do NOT name this specific claimed work (no other checked source has any text at all). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label; owner ruling G -- see 136-GATE1-DECISIONS.md § G): plausibly `confirms`, NOT a divergence -- the catalogue's own free text ('שאלות ותשובות מאת האי בן שרירא גאון') already states this claim's identification; only the structured work-id keying differed (this class's own selector over-fired here) -- confirm or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -2987,42 +3079,42 @@
       <c r="C48" s="3" t="inlineStr"/>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Allony, Nehemia Ms. 304</t>
+          <t>Ms. EVR ARAB I 1722</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>990000413480205171</t>
+          <t>990001535460205171</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): משנה תורה, ספר זמנים (w000177) / CATALOGUE NAMES (found in the identification text): הגדה של פסח (w001159)</t>
+          <t>פירוש המשנה, זרעי (w000026)</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>הגדה של פסח.</t>
+          <t>ספר תשובה. כתאב אלרד</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('הגדה של פסח') than the one this claim identifies ('משנה תורה, ספר זמנים'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `fgp_sole`: an FGP transcription's own title/author fields do NOT name this specific claimed work (no other checked source has any text at all). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3034,42 +3126,42 @@
       <c r="C49" s="3" t="inlineStr"/>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Ms. Evr. Antonin B 915</t>
+          <t>Ms. EVR ARAB I 1722</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>990000555810205171</t>
+          <t>990001535460205171</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): הלכות פסוקות (w001084) / CATALOGUE NAMES (found in the identification text): הלכות גדולות (w001196)</t>
+          <t>פירוש המשנה, מועד (w000027)</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>הלכות גדולות (בבא קמא).</t>
+          <t>ספר תשובה. כתאב אלרד</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('הלכות גדולות') than the one this claim identifies ('הלכות פסוקות'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `fgp_sole`: an FGP transcription's own title/author fields do NOT name this specific claimed work (no other checked source has any text at all). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3081,42 +3173,42 @@
       <c r="C50" s="3" t="inlineStr"/>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. Add. 3162</t>
+          <t>Ms. EVR ARAB I 1722</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>990001398690205171</t>
+          <t>990001535460205171</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): משנה תורה, ספר אהבה (w000176) / CATALOGUE NAMES (found in the identification text): ברכת המזון (w001158)</t>
+          <t>ראב"ש, שמואל א פירוש (w000046)</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>ברכת המזון.</t>
+          <t>ספר תשובה. כתאב אלרד</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ברכת המזון') than the one this claim identifies ('משנה תורה, ספר אהבה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `fgp_sole`: an FGP transcription's own title/author fields do NOT name this specific claimed work (no other checked source has any text at all). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3128,42 +3220,42 @@
       <c r="C51" s="3" t="inlineStr"/>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. Add. 1246</t>
+          <t>Ms. EVR ARAB I 1722</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>990001394270205171</t>
+          <t>990001535460205171</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): ספר יוסיפון (ערבי) (w001152) / CATALOGUE NAMES (found in the identification text): יוסיפון (w000853)</t>
+          <t>מדרש הבאור ב (w000050)</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>יוסיפון בערבית.</t>
+          <t>ספר תשובה. כתאב אלרד</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('יוסיפון') than the one this claim identifies ('ספר יוסיפון (ערבי)'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `fgp_sole`: an FGP transcription's own title/author fields do NOT name this specific claimed work (no other checked source has any text at all). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label; owner ruling G -- see 136-GATE1-DECISIONS.md § G): plausibly `confirms`, NOT a divergence -- the catalogue's own free text ('יוסיפון בערבית') already states this claim's identification; only the structured work-id keying differed (this class's own selector over-fired here) -- confirm or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3175,42 +3267,42 @@
       <c r="C52" s="3" t="inlineStr"/>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Ms. Evr. Antonin B 961</t>
+          <t>Ms. 526</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>990000555730205171</t>
+          <t>990000432020205171</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): תשובה בעניין סוכה (w000434) / CATALOGUE NAMES (found in the identification text): תשובות הגאונים (w000349)</t>
+          <t>תלמוד בבלי, תענית (w000956)</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>שאלות ותשובות הגאונים.</t>
+          <t>מעשיות מן התלמוד : ; מעשיות מן התלמוד בתרגום לערבית-יהודית.</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('תשובות הגאונים') than the one this claim identifies ('תשובה בעניין סוכה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `catalogue_sole`: this manuscript's own catalogue identification (NLI title and/or the FJMS catalog table) does NOT name this specific claimed work (no other checked source has any text at all). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3222,42 +3314,42 @@
       <c r="C53" s="3" t="inlineStr"/>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Ms. EVR ARAB I 3085</t>
+          <t>Ms. 526</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>990000801470205171</t>
+          <t>990000432020205171</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): רס"ג, ספר יצירה פירוש (w000021) / CATALOGUE NAMES (found in the identification text): ספר יצירה (w000522)</t>
+          <t>ילקוט שמעוני על נ"ך (w001383)</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>פרוש ספר יצירה בערבית.</t>
+          <t>מעשיות מן התלמוד : ; מעשיות מן התלמוד בתרגום לערבית-יהודית.</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ספר יצירה') than the one this claim identifies ('רס"ג, ספר יצירה פירוש'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `catalogue_sole`: this manuscript's own catalogue identification (NLI title and/or the FJMS catalog table) does NOT name this specific claimed work (no other checked source has any text at all). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3269,42 +3361,42 @@
       <c r="C54" s="3" t="inlineStr"/>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Catalogue Halper, Philadelphia 120</t>
+          <t>Allony, Nehemia Ms. 30g</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>990001935160205171</t>
+          <t>990000465650205171</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): הלכות פסוקות, תרגומים ועיבודים עבריים, הלכות קידושין (w001037) / CATALOGUE NAMES (found in the identification text): הלכות פסוקות (w001084)</t>
+          <t>תנ"ך, דברים (w000090)</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>הלכות פסוקות (קדושין).</t>
+          <t>תורה (דברים יד:ג-יד:כא, טז:ח-טז:יז).</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('הלכות פסוקות') than the one this claim identifies ('הלכות פסוקות, תרגומים ועיבודים עבריים, הלכות קידושין'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `catalogue_sole`: this manuscript's own catalogue identification (NLI title and/or the FJMS catalog table) does NOT name this specific claimed work (no other checked source has any text at all). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_part` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3316,42 +3408,42 @@
       <c r="C55" s="3" t="inlineStr"/>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Ms. Evr. Antonin B 236</t>
+          <t>Ms. Evr. Antonin B 1093</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>990000905560205171</t>
+          <t>990000555840205171</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): מכילתא דרבי שמעון בן יוחאי (w000321) / CATALOGUE NAMES (found in the identification text): מכילתא דרבי ישמעאל (w000766)</t>
+          <t>פרקי רבי אליעזר (w000807)</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>מכילתא דרבי ישמעאל (בא-יתרו).</t>
+          <t>תורת האדם : ; קטע מענין האבל-ענין שבתות וימים טובים. תורת האדם תורת האדם תורת האדם תורת האדם</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('מכילתא דרבי ישמעאל') than the one this claim identifies ('מכילתא דרבי שמעון בן יוחאי'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `catalogue_sole`: this manuscript's own catalogue identification (NLI title and/or the FJMS catalog table) does NOT name this specific claimed work (no other checked source has any text at all). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3363,42 +3455,42 @@
       <c r="C56" s="3" t="inlineStr"/>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Library of the Hungarian Academy of Sciences Ms. 57</t>
+          <t>Ms. EVR II A 313/22</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>990001004230205171</t>
+          <t>990000622340205171</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): ילקוט שמעוני על התורה (w001384) / CATALOGUE NAMES (found in the identification text): תנחומא (w000926)</t>
+          <t>משנה תורה, ספר אהבה (w000176)</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>מדרש תנחומא (קטעים).</t>
+          <t>משנה תורה (ספר אהבה).</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('תנחומא') than the one this claim identifies ('ילקוט שמעוני על התורה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `catalogue_sole`: this manuscript's own catalogue identification (NLI title and/or the FJMS catalog table) does NOT name this specific claimed work (no other checked source has any text at all). Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3410,42 +3502,42 @@
       <c r="C57" s="3" t="inlineStr"/>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S NS 169.52</t>
+          <t>Ms. 523</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>990051091870205171</t>
+          <t>990000432000205171</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): נסים גאון, חמשה ספרים (w000071) / CATALOGUE NAMES (found in the identification text): מגילת סתרים (w000509)</t>
+          <t>משנה, מעשרות (w000264)</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>הלכה; מגילת סתרים [נסים בן יעקב]; ספרות הלכתית ופרשנות תלמודית; ספרות חז"ל. ; Halakhic Literature and Talmudic Commentaries ; Rabbinica; exposition of PT hagigah 78a and Tosefta Sheqalim 3:23-24 (the latter section numbered 140).</t>
+          <t>משנה סדר זרעים (קטעים) : ; קטע ממס' מעשר-שני, מעשרות, קטע ממס' חלה. עם טעמים וניקוד חלקי. משנה [טקסט] Mishnah [Text] משנה [טקסט] Mishnah [Text]</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('מגילת סתרים') than the one this claim identifies ('נסים גאון, חמשה ספרים'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `multi_source`: &gt;=2 checked sources have text for this manuscript, but NONE of them names this specific claimed work. Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3457,42 +3549,42 @@
       <c r="C58" s="3" t="inlineStr"/>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S F 7.45</t>
+          <t>Ms. 523</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>990051173260205171</t>
+          <t>990000432000205171</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): משנה תורה, הקדמה ומניין המצוות (w000174) / CATALOGUE NAMES (found in the identification text): הלכות ציצית (w001052)</t>
+          <t>משנה, מעשר שני (w000265)</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>משנה תורה;משנה תורה ופירושיו. ; Mishneh Torah and its Commentaries ; מנין מצות על סדר הרמב"ם, מסוף ספר אהבה (הלכות ציצית) עד סוף ספר זמנים</t>
+          <t>משנה סדר זרעים (קטעים) : ; קטע ממס' מעשר-שני, מעשרות, קטע ממס' חלה. עם טעמים וניקוד חלקי. משנה [טקסט] Mishnah [Text] משנה [טקסט] Mishnah [Text]</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('הלכות ציצית') than the one this claim identifies ('משנה תורה, הקדמה ומניין המצוות'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `multi_source`: &gt;=2 checked sources have text for this manuscript, but NONE of them names this specific claimed work. Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_part` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3504,42 +3596,42 @@
       <c r="C59" s="3" t="inlineStr"/>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Ms. EVR II A 33</t>
+          <t>Ms. 523</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>990000621960205171</t>
+          <t>990000432000205171</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): תנ"ך, בראשית (w000086) / CATALOGUE NAMES (found in the identification text): שאילתות (w000732)</t>
+          <t>משנה, חלה (w000266)</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>שאילתות.</t>
+          <t>משנה סדר זרעים (קטעים) : ; קטע ממס' מעשר-שני, מעשרות, קטע ממס' חלה. עם טעמים וניקוד חלקי. משנה [טקסט] Mishnah [Text] משנה [טקסט] Mishnah [Text]</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('שאילתות') than the one this claim identifies ('תנ"ך, בראשית'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `multi_source`: &gt;=2 checked sources have text for this manuscript, but NONE of them names this specific claimed work. Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3551,42 +3643,42 @@
       <c r="C60" s="3" t="inlineStr"/>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S C 1.23</t>
+          <t>Constantin von Tischendorf Collection Ms. 43</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>990051150540205171</t>
+          <t>990000571680205171</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): בראשית רבה צה-צו, תוספת (w000900) / CATALOGUE NAMES (found in the identification text): בראשית רבה (w000156)</t>
+          <t>תנ"ך, יהושע (w000091)</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>בראשית רבה;מדרש. ; Midrash ; בראשית רבה</t>
+          <t>נביאים ראשונים (קטעים) : ; עם ניקוד וטעמים, מסורה קטנה וגדולה. מקרא [טקסט] Bible [Text]</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('בראשית רבה') than the one this claim identifies ('בראשית רבה צה-צו, תוספת'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `multi_source`: &gt;=2 checked sources have text for this manuscript, but NONE of them names this specific claimed work. Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_part` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
@@ -3598,1321 +3690,52 @@
       <c r="C61" s="3" t="inlineStr"/>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Cambridge University Library Ms. T-S Misc. 15.67</t>
+          <t>Constantin von Tischendorf Collection Ms. 43</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>990051080280205171</t>
+          <t>990000571680205171</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>CLAIMED (this identification): ויקרא רבה (w000169) / CATALOGUE NAMES (found in the identification text): חובות הלבבות (תרגום אבן תיבון) (w000195)</t>
+          <t>תנ"ך, שופטים (w000092)</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>חובות הלבבות (תרגום אבן תיבון). ; ספר חובות הלבבות. מעלת התשובה ומעלת הצדקה. דפוס.</t>
+          <t>נביאים ראשונים (קטעים) : ; עם ניקוד וטעמים, מסורה קטנה וגדולה. מקרא [טקסט] Bible [Text]</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('חובות הלבבות (תרגום אבן תיבון)') than the one this claim identifies ('ויקרא רבה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
+          <t>Residual stratum `multi_source`: &gt;=2 checked sources have text for this manuscript, but NONE of them names this specific claimed work. Under owner ruling J's funnel-first architecture, this row WOULD reach the pinned model gate.</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>PROPOSAL (draft, not a label; owner ruling F -- see 136-GATE1-DECISIONS.md § F): plausibly `diverges_work` -- confirm the shade AND supply the separate Correctness call (catalogue_correct / claim_correct / unclear), or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr"/>
-      <c r="C62" s="3" t="inlineStr"/>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>Library of the Alliance Israélite Un Ms. III A 101</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>990001506030205171</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): רי"ף ברכות (w001317) / CATALOGUE NAMES (found in the identification text): מסכת דרך ארץ זוטא (w000787)</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>מסכת דרך ארץ זוטא (פרק השלום).</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('מסכת דרך ארץ זוטא') than the one this claim identifies ('רי"ף ברכות'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="B63" s="3" t="inlineStr"/>
-      <c r="C63" s="3" t="inlineStr"/>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>Cambridge University Library Ms. T-S C 1.19</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>990051150500205171</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): פסיקתא דרב כהנא (w000904) / CATALOGUE NAMES (found in the identification text): ויקרא רבה (w000169)</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>ויקרא רבה;מדרש. ; Midrash ; ויקרא רבה</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ויקרא רבה') than the one this claim identifies ('פסיקתא דרב כהנא'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="B64" s="3" t="inlineStr"/>
-      <c r="C64" s="3" t="inlineStr"/>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>Cambridge University Library Ms. T-S NS 291.103</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>990051104680205171</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): רד"ק על יחזקאל (w001245) / CATALOGUE NAMES (found in the identification text): מדרש תהלים (w001124)</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>מדרש תהלים; ספרות הלכתית ופרשנות תלמודית; ספרות חז"ל; פירוש רד"ק למקרא. ; דוד בן יוסף קמחי, פירוש רד"ק למקרא: יחזקאל ח:א – יא</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('מדרש תהלים') than the one this claim identifies ('רד"ק על יחזקאל'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="B65" s="3" t="inlineStr"/>
-      <c r="C65" s="3" t="inlineStr"/>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>Adler, Elkan Nathan Ms. 2160.12</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>990053147670205171</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): רס"ג, איכה תרגום (w000012) / CATALOGUE NAMES (found in the identification text): תרגום איכה (w001413)</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>מקרא [טקסט];תפסיר ערבי. ; תרגום איכה ד:א-כא לערבית-יהודית</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('תרגום איכה') than the one this claim identifies ('רס"ג, איכה תרגום'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B66" s="3" t="inlineStr"/>
-      <c r="C66" s="3" t="inlineStr"/>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>Ms. EVR ARAB I 1771</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>990001535860205171</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): ראב"ש, שמואל א פירוש (w000046) / CATALOGUE NAMES (found in the identification text): ספר הרקמה (w000037)</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>כתאב אלאסל : ; ספר הרקמה בערבית.</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ספר הרקמה') than the one this claim identifies ('ראב"ש, שמואל א פירוש'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="B67" s="3" t="inlineStr"/>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>Cambridge University Library Ms. T-S E 1.2</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>990051158320205171</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): משנה, פאה (w000259) / CATALOGUE NAMES (found in the identification text): ברייתא דמלאכת המשכן (w000157)</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>ברייתא דמלאכת המשכן;מסכת גרים;משנה [טקסט]. ; Mishnah: Pe'ah 4:4 – 6:3; Berakhot 1:1 – 3:1 ; משנה: פאה ד:ד – ו:ג; ברכות א:א – ג:א</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ברייתא דמלאכת המשכן') than the one this claim identifies ('משנה, פאה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="B68" s="3" t="inlineStr"/>
-      <c r="C68" s="3" t="inlineStr"/>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>Cambridge University Library Ms. T-S C 6.113</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>990051154860205171</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): תלמוד בבלי, מגילה (w000957) / CATALOGUE NAMES (found in the identification text): ספרי דברים (w000166)</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>ספרי דברים;פירוש אבן עזרא למקרא;פרשנות מקרא. ; Sifre on Deuteronomy: 11:399 – 15:400; 7:404 – 15:400[בדילוגים] ; ספרי דברים: יא:399 – טו:400; ז:404 – טו:400[בדילוגים]</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ספרי דברים') than the one this claim identifies ('תלמוד בבלי, מגילה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="B69" s="3" t="inlineStr"/>
-      <c r="C69" s="3" t="inlineStr"/>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>Cambridge University Library Ms. T-S F 17.48</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>990051180030205171</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): ויקרא רבה (w000169) / CATALOGUE NAMES (found in the identification text): קהלת רבה (w000891)</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>קהלת רבה;תלמוד ירושלמי [טקסט]. ; Midrash Rabbah Ecclesiastes: 5 ; קהלת רבה: ה</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('קהלת רבה') than the one this claim identifies ('ויקרא רבה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="B70" s="3" t="inlineStr"/>
-      <c r="C70" s="3" t="inlineStr"/>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>Cambridge University Library Ms. T-S F 2(2).64</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>990051167990205171</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): תלמוד בבלי, עבודה זרה (w000973) / CATALOGUE NAMES (found in the identification text): פסיקתא דרב כהנא (w000904)</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>מדרש;פסיקתא דרב כהנא;תלמוד בבלי [טקסט]. ; Talmud Bavli: Niddah 31 a – b; Sotah 44 b – 45 b; Avodah Zarah 51 a – 52 b ; תלמוד בבלי: נידה לא ע"א – ע"ב; סוטה מד ע"ב – מה ע"ב; עבודה זרה נא ע"א – נב ע"ב</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('פסיקתא דרב כהנא') than the one this claim identifies ('תלמוד בבלי, עבודה זרה'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="B71" s="3" t="inlineStr"/>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>Cambridge University Library Ms. L-G Talm. I 45</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>990001842460205171</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): הלכות ארץ ישראליות ובבליות וליקוטים ממעשים לבני ארץ ישראל (w001075) / CATALOGUE NAMES (found in the identification text): מעשים לבני ארץ ישראל (w001030)</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>מעשים לבני ארץ ישראל.</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('מעשים לבני ארץ ישראל') than the one this claim identifies ('הלכות ארץ ישראליות ובבליות וליקוטים ממעשים לבני ארץ ישראל'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="B72" s="3" t="inlineStr"/>
-      <c r="C72" s="3" t="inlineStr"/>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>MS heb. e.22/1</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>990053426460205171</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): הלכות פסוקות (w001084) / CATALOGUE NAMES (found in the identification text): והזהיר (w000779)</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>ספר והזהיר. ; והזהיר, פסק"ז</t>
-        </is>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('והזהיר') than the one this claim identifies ('הלכות פסוקות'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="B73" s="3" t="inlineStr"/>
-      <c r="C73" s="3" t="inlineStr"/>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>Cambridge University Library Ms. T-S NS 309.81</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>990051106940205171</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): מסכת דרך ארץ זוטא (w000787) / CATALOGUE NAMES (found in the identification text): מסכת דרך ארץ רבה (w000786)</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>מסכת דרך ארץ רבה; סידור שלמה מסיג'ילמאסה; ספרות הלכתית ופרשנות תלמודית; ספרות חז"ל; קולופון. ; Halakhic Literature and Talmudic Commentaries ; שלמה בן נתן מסיג'ילמאסה, סידור שלמה מסיג'ילמאסה: ל</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('מסכת דרך ארץ רבה') than the one this claim identifies ('מסכת דרך ארץ זוטא'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="B74" s="3" t="inlineStr"/>
-      <c r="C74" s="3" t="inlineStr"/>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>Adler, Elkan Nathan Ms. 2700.24</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>990053586310205171</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): פירוש המשנה, נזיקין (w000028) / CATALOGUE NAMES (found in the identification text): משנה, סנהדרין (w000291)</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>משנה [טקסט];פירוש המשנה לרמב"ם [ערבית]. ; פירוש הרמב"ם למשנה, סנהדרין י:א, ההקדמה לפרק חלק, עיקרים ראשון ושני (מהד' קאפח ע' רי-ריא).</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('משנה, סנהדרין') than the one this claim identifies ('פירוש המשנה, נזיקין'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="B75" s="3" t="inlineStr"/>
-      <c r="C75" s="3" t="inlineStr"/>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>Cambridge University Library Ms. T-S C 1.60</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>990051150910205171</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): ברייתא דישועה, הפירוש, נוסח אחר (w000755) / CATALOGUE NAMES (found in the identification text): ברייתא דישועה (w000754)</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>ברייתא דישועה;מדרש. ; Midrash ; ברייתא דישועה</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('ברייתא דישועה') than the one this claim identifies ('ברייתא דישועה, הפירוש, נוסח אחר'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="B76" s="3" t="inlineStr"/>
-      <c r="C76" s="3" t="inlineStr"/>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>Cambridge University Library Ms. T-S NS 329/0609</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>990001420410205171</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>CLAIMED (this identification): פסיקתא, ״אנכי אדוני אלהיך״ (איש שלום צח) (w000506) / CATALOGUE NAMES (found in the identification text): פסיקתא רבתי (w000803)</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>פסיקתא רבתי (פרשה כג:ו) :</t>
-        </is>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a DIFFERENT work ('פסיקתא רבתי') than the one this claim identifies ('פסיקתא, ״אנכי אדוני אלהיך״ (איש שלום צח)'); the two are NOT a granularity variant under the D-13d author-gated rule (different author, or an unrelated title) -- a genuine catalogue/claim divergence CANDIDATE (owner ruling F splits the shade into `diverges_work` / `diverges_part` by scope; owner ruling G warns this selector can over-fire when the catalogue's free text actually already agrees with the claim under a different structured key -- see the Vocabulary sheet/table).</t>
-        </is>
-      </c>
-      <c r="K76" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label): plausibly `diverges_work` or `diverges_part` (scope not yet distinguished by owner rulings F/G for this specific case) -- the catalogue and this claim name different works or parts; per ruling G, first check whether the catalogue's own FREE TEXT already states this claim's identification under a different spelling/phrasing before confirming a divergence -- confirm the shade, the scope, and (if divergent) the Correctness call, or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="B77" s="3" t="inlineStr"/>
-      <c r="C77" s="3" t="inlineStr"/>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>Cambridge University Library Ms. Add. 3356</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>990001398970205171</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך, תהלים (w000112)</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>מחזור מנהג ארץ ישראל הקדמון.</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'מחזור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="B78" s="3" t="inlineStr"/>
-      <c r="C78" s="3" t="inlineStr"/>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>Cambridge University Library Ms. T-S Misc. 33/03</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>990001413070205171</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך, שמות (w000087)</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>מחזור מנהג אשכנז לשלש רגלים : ; קטעי גניזה.</t>
-        </is>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'מחזור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="B79" s="3" t="inlineStr"/>
-      <c r="C79" s="3" t="inlineStr"/>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>Ms. EVR II A 58</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>990001429050205171</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך, ישעיהו (w000097)</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>מחזור מנהג ספרד לשלש רגלים.</t>
-        </is>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'מחזור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="B80" s="3" t="inlineStr"/>
-      <c r="C80" s="3" t="inlineStr"/>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>Ms. EVR II A 300/4</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t>990001436770205171</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך, דברים (w000090)</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>סדור מנהג קראים.</t>
-        </is>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
-        </is>
-      </c>
-      <c r="K80" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="B81" s="3" t="inlineStr"/>
-      <c r="C81" s="3" t="inlineStr"/>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>Ms. EVR II A 810</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>990001442520205171</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך, ויקרא (w000088)</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>סדור מנהג קראים (קטע).</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="B82" s="3" t="inlineStr"/>
-      <c r="C82" s="3" t="inlineStr"/>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t>Ms. EVR II A 1006</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>990001444570205171</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך, יחזקאל (w000099)</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>סדור מנהג קראים.</t>
-        </is>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
-        </is>
-      </c>
-      <c r="K82" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="B83" s="3" t="inlineStr"/>
-      <c r="C83" s="3" t="inlineStr"/>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>Ms. EVR II A 642</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>990001441300205171</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך, במדבר (w000089)</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>סדור מנהג קראים (קטע).</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="B84" s="3" t="inlineStr"/>
-      <c r="C84" s="3" t="inlineStr"/>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>Library of the Hungarian Academy of Sciences Ms. 116</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>990001035960205171</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>משנה תורה, ספר אהבה (w000176)</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>מחזור מנהג ספרד לראש השנה (קטע).</t>
-        </is>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'מחזור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="B85" s="3" t="inlineStr"/>
-      <c r="C85" s="3" t="inlineStr"/>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>Ms. EVR II A 834</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>990001442760205171</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך, ירמיהו (w000098)</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>סדור מנהג קראים (קטעים).</t>
-        </is>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B86" s="3" t="inlineStr"/>
-      <c r="C86" s="3" t="inlineStr"/>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>Ms. EVR II A 2007</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>990001454910205171</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך, דניאל (w000120)</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr">
-        <is>
-          <t>סדור מנהג קראים (קטעים).</t>
-        </is>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="B87" s="3" t="inlineStr"/>
-      <c r="C87" s="3" t="inlineStr"/>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>Ms. EVR II A 2060</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>990001455500205171</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך, דברי הימים ב (w000124)</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>סדור מנהג קראים (קטעים).</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
-        </is>
-      </c>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B88" s="3" t="inlineStr"/>
-      <c r="C88" s="3" t="inlineStr"/>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>Ms. EVR II A 867</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t>990001443150205171</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך, דברי הימים א (w000123)</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t>סדור מנהג קראים (קטעים).</t>
-        </is>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>This manuscript's own catalogue identification text names a SPECIFIC, NAMED standard-rite prayer-book/cycle (a container collocation: 'סדור מנהג'), whose standard, predictable content plausibly includes this specific claimed unit -- without the catalogue text ever naming the unit itself. Under the pre-H shade enum this would fall through to `fills_gap` by elimination, which would publish a standard siddur/machzor component as a candidate new find.</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSAL (draft, not a label; owner ruling H -- see 136-GATE1-DECISIONS.md § H): plausibly `container_predicts` -- confirm or correct.</t>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `fills_gap` -- confirm or correct.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K88"/>
+  <autoFilter ref="A1:K61"/>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B88" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid verdict" error="Choose one of the listed shades, or 'unsure' / 'skip'. Free text is rejected." promptTitle="Shade verdict" prompt="Pick the shade that best fits, or 'unsure' / 'skip'. Blank = not yet answered." type="list">
+    <dataValidation sqref="B2:B61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid verdict" error="Choose one of the listed shades, or 'unsure' / 'skip'. Free text is rejected." promptTitle="Shade verdict" prompt="Pick the shade that best fits, or 'unsure' / 'skip'. Blank = not yet answered." type="list">
       <formula1>"confirms,refines_granularity,aid_more_specific,diverges_work,diverges_part,container_predicts,fills_gap,extends,alias_merge,unsure,skip"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C88" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid correctness call" error="Choose 'catalogue_correct', 'claim_correct' or 'unclear', or leave blank." promptTitle="Correctness (divergence rows only)" prompt="Only answer if the Shade verdict is diverges_work or diverges_part. Otherwise leave blank." type="list">
+    <dataValidation sqref="C2:C61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid correctness call" error="Choose 'catalogue_correct', 'claim_correct' or 'unclear', or leave blank." promptTitle="Correctness (divergence rows only)" prompt="Only answer if the Shade verdict is diverges_work or diverges_part. Otherwise leave blank." type="list">
       <formula1>"catalogue_correct,claim_correct,unclear"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4926,7 +3749,1536 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Case #</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Demotion verdict</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Stratum</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Manuscript</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sys_id</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Claimed work</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Catalogue's own identification text</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Why this demotion is being checked</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft -- NOT a label)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>published_full_sole</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Allony, Nehemia Ms. 113</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>990000465700205171</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>הלכות גדולות (w001196)</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>כתאב אלנפקאת (קטע). כתאב אלנפקאת</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `published_full_sole`: the CURRENT heuristic treats ANY bibliography row with TranscriptionType='Full' as naming this claim, regardless of whether that row's own title/author actually matches (Codex finding 1) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>published_full_sole</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Ms. Evr. Antonin B 1037</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>990000555740205171</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>תשובות שמואל גאון (w000428)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>שאלות ותשובות הגאונים.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `published_full_sole`: the CURRENT heuristic treats ANY bibliography row with TranscriptionType='Full' as naming this claim, regardless of whether that row's own title/author actually matches (Codex finding 1) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>published_full_sole</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Ms. Evr. Antonin B 292</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>990000555790205171</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>במדבר רבה א-יד (w000496)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>אבות דרבי נתן נוסח א : ; קטעים מפרקים א-ב. אבות דרבי נתן, נוסחא א Avot de-Rabbi Natan I אבות דרבי נתן, נוסחא א Avot de-Rabbi Natan I אבות דרבי נתן, נוסחא א Avot de-Rabbi Natan I אבות דרבי נתן, נוסחא א Avot de-Rabbi Natan I אבות דרבי נתן, נוסחא א Avot de-Rabbi Natan I אבות דרבי נתן, נוסחא א Avot de-Rabbi Natan I אבות דרבי נתן Avot de-Rabbi Natan אבות דרבי נתן Avot de-Rabbi Natan אבות דרבי נתן, נוסחא א Avot de-Rabbi Natan I</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `published_full_sole`: the CURRENT heuristic treats ANY bibliography row with TranscriptionType='Full' as naming this claim, regardless of whether that row's own title/author actually matches (Codex finding 1) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>published_full_sole</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR ARAB I 1467</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>990000635630205171</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>הלכות גדולות (w001196)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>קובץ חבורי הלכה מאת שמואל בן חפני גאון בשפה הערבית. כתאב אלשפעה כתאב אחכאם שרע אלציצית כתאב אלבלוג כתאב אלבלוג ואל אדראך כתאב אחכאם שרע אלציצית כתאב אלשפעה</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `published_full_sole`: the CURRENT heuristic treats ANY bibliography row with TranscriptionType='Full' as naming this claim, regardless of whether that row's own title/author actually matches (Codex finding 1) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>published_full_sole</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR ARAB I 1793</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>990000635770205171</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>משנה, ראש השנה (w000276)</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>כתאב אלאסתבצאר : ; בערבית. כתאב אלאסתבצאר</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `published_full_sole`: the CURRENT heuristic treats ANY bibliography row with TranscriptionType='Full' as naming this claim, regardless of whether that row's own title/author actually matches (Codex finding 1) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>published_full_sole</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II A 85/14</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>990000847320205171</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>אגרות הרמב״ם (שילת) (w001140)</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>מקמה (קטע).</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `published_full_sole`: the CURRENT heuristic treats ANY bibliography row with TranscriptionType='Full' as naming this claim, regardless of whether that row's own title/author actually matches (Codex finding 1) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>published_full_sole</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II A 380</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>990000848410205171</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>הכוזרי (w000053)</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>קובץ בהגות. זוהר</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `published_full_sole`: the CURRENT heuristic treats ANY bibliography row with TranscriptionType='Full' as naming this claim, regardless of whether that row's own title/author actually matches (Codex finding 1) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>published_full_sole</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II A 380</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>990000848410205171</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>ספר יצירה (w000522)</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>קובץ בהגות. זוהר</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `published_full_sole`: the CURRENT heuristic treats ANY bibliography row with TranscriptionType='Full' as naming this claim, regardless of whether that row's own title/author actually matches (Codex finding 1) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>published_full_sole</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR ARAB I 4633</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>990000854530205171</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, בראשית (w000086)</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>פרוש התורה (בראשית). פירוש על התורה פירוש על התורה</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `published_full_sole`: the CURRENT heuristic treats ANY bibliography row with TranscriptionType='Full' as naming this claim, regardless of whether that row's own title/author actually matches (Codex finding 1) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>published_full_sole</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR ARAB I 1687</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>990000854930205171</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>משנה, ראש השנה (w000276)</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>כתאב אלאנואר ואלמראקב (קטעים). כתאב אלאנואר ואלמראקב כתאב אלאנואר ואלמראקב</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `published_full_sole`: the CURRENT heuristic treats ANY bibliography row with TranscriptionType='Full' as naming this claim, regardless of whether that row's own title/author actually matches (Codex finding 1) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>pgp_sole</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II B 159</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>990000571710205171</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, דברים (w000090)</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>תורה (דברים לא:י-לד:יב) : ; עם ניקוד וטעמים, מסורה קטנה וגדולה. מקרא [טקסט] Bible [Text]</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `pgp_sole`: the CURRENT heuristic treats ANY PGP document with a non-empty description or transcription as naming this claim, regardless of whether that text actually names this specific work (Codex finding 6) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>pgp_sole</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II B 25</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>990000571720205171</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, יהושע (w000091)</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>נביאים (קטעים). מקרא [טקסט] Bible [Text] מקרא [טקסט] Bible [Text]</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `pgp_sole`: the CURRENT heuristic treats ANY PGP document with a non-empty description or transcription as naming this claim, regardless of whether that text actually names this specific work (Codex finding 6) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>pgp_sole</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II B 25</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>990000571720205171</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, שופטים (w000092)</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>נביאים (קטעים). מקרא [טקסט] Bible [Text] מקרא [טקסט] Bible [Text]</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `pgp_sole`: the CURRENT heuristic treats ANY PGP document with a non-empty description or transcription as naming this claim, regardless of whether that text actually names this specific work (Codex finding 6) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>pgp_sole</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II B 25</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>990000571720205171</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, שמואל א (w000093)</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>נביאים (קטעים). מקרא [טקסט] Bible [Text] מקרא [טקסט] Bible [Text]</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `pgp_sole`: the CURRENT heuristic treats ANY PGP document with a non-empty description or transcription as naming this claim, regardless of whether that text actually names this specific work (Codex finding 6) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>pgp_sole</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II B 25</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>990000571720205171</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, שמואל ב (w000094)</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>נביאים (קטעים). מקרא [טקסט] Bible [Text] מקרא [טקסט] Bible [Text]</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `pgp_sole`: the CURRENT heuristic treats ANY PGP document with a non-empty description or transcription as naming this claim, regardless of whether that text actually names this specific work (Codex finding 6) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>pgp_sole</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II B 25</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>990000571720205171</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, מלכים א (w000095)</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>נביאים (קטעים). מקרא [טקסט] Bible [Text] מקרא [טקסט] Bible [Text]</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `pgp_sole`: the CURRENT heuristic treats ANY PGP document with a non-empty description or transcription as naming this claim, regardless of whether that text actually names this specific work (Codex finding 6) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>pgp_sole</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II B 25</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>990000571720205171</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, מלכים ב (w000096)</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>נביאים (קטעים). מקרא [טקסט] Bible [Text] מקרא [טקסט] Bible [Text]</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `pgp_sole`: the CURRENT heuristic treats ANY PGP document with a non-empty description or transcription as naming this claim, regardless of whether that text actually names this specific work (Codex finding 6) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>pgp_sole</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II B 25</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>990000571720205171</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, ישעיהו (w000097)</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>נביאים (קטעים). מקרא [טקסט] Bible [Text] מקרא [טקסט] Bible [Text]</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `pgp_sole`: the CURRENT heuristic treats ANY PGP document with a non-empty description or transcription as naming this claim, regardless of whether that text actually names this specific work (Codex finding 6) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>pgp_sole</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II B 25</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>990000571720205171</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, דברי הימים ב (w000124)</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>נביאים (קטעים). מקרא [טקסט] Bible [Text] מקרא [טקסט] Bible [Text]</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `pgp_sole`: the CURRENT heuristic treats ANY PGP document with a non-empty description or transcription as naming this claim, regardless of whether that text actually names this specific work (Codex finding 6) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>pgp_sole</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Ms. EVR II B 1283</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>990000571850205171</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, ישעיהו (w000097)</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>נביאים אחרונים (קטעים). מקרא [טקסט] Bible [Text]</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `pgp_sole`: the CURRENT heuristic treats ANY PGP document with a non-empty description or transcription as naming this claim, regardless of whether that text actually names this specific work (Codex finding 6) -- no OTHER checked source agrees.</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>other_demotion</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Ms. Evr. Antonin B 308</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>990000555750205171</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>תשובות שר שלום גאון (w000499)</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>שאלות ותשובות הגאונים.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `other_demotion`: a genuine token-name-match (catalogue, FGP, or bib known_bib) demotes this claim -- included for comparison against the two oversampled over-broad categories above.</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>other_demotion</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Ms. Evr. Antonin B 297</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>990000555760205171</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>מסכת אבות דרבי נתן, נוסח ב (w000789)</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>אבות דרבי נתן נוסח ב : ; קטע מפרקים ד-ז. אבות דרבי נתן, נוסחא א Avot de-Rabbi Natan I אבות דרבי נתן, נוסחא ב Avot de-Rabbi Natan II אבות דרבי נתן Avot de-Rabbi Natan אבות דרבי נתן, נוסחא א Avot de-Rabbi Natan I אבות דרבי נתן, נוסחא ב Avot de-Rabbi Natan II אבות דרבי נתן, נוסחא ב Avot de-Rabbi Natan II אבות דרבי נתן Avot de-Rabbi Natan אבות דרבי נתן Avot de-Rabbi Natan אבות דרבי נתן, נוסחא ב Avot de-Rabbi Natan II</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `other_demotion`: a genuine token-name-match (catalogue, FGP, or bib known_bib) demotes this claim -- included for comparison against the two oversampled over-broad categories above.</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>other_demotion</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Ms. Evr. Antonin B 249</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>990000555770205171</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>מסכת אבות דרבי נתן, נוסח ב (w000789)</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>אבות דרבי נתן נוסח ב : ; כולל קטעים מפרק מג, רובו של פרק מו ותחילת פרק מז. אבות דרבי נתן, נוסחא ב Avot de-Rabbi Natan II אבות דרבי נתן, נוסחא ב Avot de-Rabbi Natan II אבות דרבי נתן, נוסחא ב Avot de-Rabbi Natan II אבות דרבי נתן, נוסחא ב Avot de-Rabbi Natan II אבות דרבי נתן, נוסחא ב Avot de-Rabbi Natan II אבות דרבי נתן Avot de-Rabbi Natan אבות דרבי נתן Avot de-Rabbi Natan אבות דרבי נתן Avot de-Rabbi Natan אבות דרבי נתן, נוסחא ב Avot de-Rabbi Natan II</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `other_demotion`: a genuine token-name-match (catalogue, FGP, or bib known_bib) demotes this claim -- included for comparison against the two oversampled over-broad categories above.</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>other_demotion</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Ms. Evr. Antonin B 902</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>990000555800205171</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>הלכות ראו (w000797)</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>הלכות ראו (אבל-מועד) : ; הוא התרגום העברי של הלכות פסוקות. הלכות פסוקות Halakhot Pesuqot הלכות פסוקות Halakhot Pesuqot</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `other_demotion`: a genuine token-name-match (catalogue, FGP, or bib known_bib) demotes this claim -- included for comparison against the two oversampled over-broad categories above.</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>other_demotion</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Ms. Evr. Antonin B 276</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>990000555830205171</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>הלכות גדולות (w001196)</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>הלכות גדולות (קטע). הלכות גדולות Halakhot Gedolot הלכות גדולות Halakhot Gedolot הלכות גדולות Halakhot Gedolot הלכות גדולות Halakhot Gedolot</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Demotion stratum `other_demotion`: a genuine token-name-match (catalogue, FGP, or bib known_bib) demotes this claim -- included for comparison against the two oversampled over-broad categories above.</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSAL (draft, not a label; owner ruling J -- see 136-GATE1-DECISIONS.md § J): plausibly `demotion_correct` -- confirm or correct to `false_known` if the demoting source does not actually name this specific work.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J26"/>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid demotion verdict" error="Choose 'demotion_correct', 'false_known', 'unsure' or 'skip'. Free text is rejected." promptTitle="Demotion verdict" prompt="Does the demoting source genuinely name THIS specific work? Blank = not yet answered." type="list">
+      <formula1>"demotion_correct,false_known,unsure,skip"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Case #</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Manuscript</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sys_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Claimed work</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Why no verdict is collected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Arm 3 -- NO-SOURCE-TEXT: rows shipped as candidates with no verdict (owner ruling J)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Cambridge University Library Ms. T-S Misc. 34.20</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>990051124460205171</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>רס"ג, שמות תרגום (תפסיר תורה) (w000033)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>None of the four checked-source families (bib, PGP, FGP, catalogue) has ANY text at all for this manuscript -- this row ships as a novelty candidate automatically, with no source to check it against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Arm 3 -- NO-SOURCE-TEXT: rows shipped as candidates with no verdict (owner ruling J)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Cambridge University Library Ms. T-S Misc. 34.23</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>990051124490205171</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>משנה תורה, ספר אהבה (w000176)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>None of the four checked-source families (bib, PGP, FGP, catalogue) has ANY text at all for this manuscript -- this row ships as a novelty candidate automatically, with no source to check it against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Arm 3 -- NO-SOURCE-TEXT: rows shipped as candidates with no verdict (owner ruling J)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Cambridge University Library Ms. T-S Misc. 34.29</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>990051124550205171</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, בראשית (w000086)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>None of the four checked-source families (bib, PGP, FGP, catalogue) has ANY text at all for this manuscript -- this row ships as a novelty candidate automatically, with no source to check it against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Arm 3 -- NO-SOURCE-TEXT: rows shipped as candidates with no verdict (owner ruling J)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Cambridge University Library Ms. T-S K 27.26</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>990051220440205171</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>הלכות גדולות (w001196)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>None of the four checked-source families (bib, PGP, FGP, catalogue) has ANY text at all for this manuscript -- this row ships as a novelty candidate automatically, with no source to check it against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Arm 3 -- NO-SOURCE-TEXT: rows shipped as candidates with no verdict (owner ruling J)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Cambridge University Library Ms. T-S K 27.28</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>990051220460205171</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>מדרש אגור (w000836)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>None of the four checked-source families (bib, PGP, FGP, catalogue) has ANY text at all for this manuscript -- this row ships as a novelty candidate automatically, with no source to check it against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Arm 3 -- NO-SOURCE-TEXT: rows shipped as candidates with no verdict (owner ruling J)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Cambridge University Library Ms. T-S K 27.39</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>990051220580205171</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>סדר אליהו זוטא א-טו (w000162)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>None of the four checked-source families (bib, PGP, FGP, catalogue) has ANY text at all for this manuscript -- this row ships as a novelty candidate automatically, with no source to check it against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Arm 3 -- NO-SOURCE-TEXT: rows shipped as candidates with no verdict (owner ruling J)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Cambridge University Library Ms. T-S K 27.41</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>990051220600205171</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך, ויקרא (w000088)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>None of the four checked-source families (bib, PGP, FGP, catalogue) has ANY text at all for this manuscript -- this row ships as a novelty candidate automatically, with no source to check it against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Arm 3 -- NO-SOURCE-TEXT: rows shipped as candidates with no verdict (owner ruling J)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Cambridge University Library Ms. T-S K 27.42</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>990051220610205171</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>דברי הימים של משה רבנו (w000944)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>None of the four checked-source families (bib, PGP, FGP, catalogue) has ANY text at all for this manuscript -- this row ships as a novelty candidate automatically, with no source to check it against.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4936,385 +5288,453 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>This workbook is a labelling instrument for the novelty hard-case evaluation set (plan 136-03 Task 3). The Markdown file 136-NOVELTY-HARDCASES.md in the same phase directory remains the authoritative human-readable record of these 95 candidate cases and the reasoning for why each is hard; this workbook renders the SAME cases, in the SAME order, from one shared pre-numbered case list, split across two data sheets by the question type each case was actually built to support.</t>
+          <t>This workbook is a labelling instrument for the novelty hard-case evaluation set (plan 136-03 Task 3). The Markdown file 136-NOVELTY-HARDCASES.md in the same phase directory remains the authoritative human-readable record of these 101 candidate cases and the reasoning for why each is hard; this workbook renders the SAME cases, in the SAME order, from one shared pre-numbered case list, split across four data sheets by the question type each class/arm was actually built to support.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>"Identity Spot-Check" (Classes 1-3): these rows compare two of OUR OWN claims to each other -- an A vs B "same underlying work?" judgment, no finding aid involved at all. "Novelty Shades" (Classes 4-7): these rows judge ONE claim against the finding aids -- the question genuinely varies here, which is why it carries the fuller shade vocabulary plus a Correctness column for divergence rows.</t>
+          <t>"Identity Spot-Check" (Classes 1-3, UNCHANGED): these rows compare two of OUR OWN claims to each other -- an A vs B "same underlying work?" judgment, no finding aid involved at all. "Novelty Shades" (Class 6, unchanged, + Arm 1 residual): these rows judge ONE claim against the finding aids, with the full ten-shade vocabulary plus a Correctness column for Class 6 divergence rows. "Heuristic-Demoted" (Arm 2, NEW): rows the funnel already marked known BEFORE any model call -- judge whether that demotion is correct. "No-Source-Text" (Arm 3, NEW): informational only, no verdict collected -- see its own note below.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>IMPORTANT: a BLANK verdict cell (Identity OR Shade) is NOT a label -- it means "not yet answered". If you cannot judge a case, enter `unsure` explicitly (it costs nothing and is a real, useful answer) rather than leaving the cell blank. If you choose not to judge a case at all, enter `skip` explicitly -- it is recorded as skipped, never silently filled from the case's own draft PROPOSAL. The Correctness column is meaningful ONLY when the Shade verdict is `diverges_work` or `diverges_part` -- leave it blank on every other row.</t>
+          <t>Owner ruling J (136-GATE1-DECISIONS.md § J, 2026-08-02) replaced the former Classes 4/5/7 with a three-arm, SOURCE-STRATIFIED sample after a prior-art pass found those selectors read ONLY libraries.csv column 7 -- zero representation of the bib/PGP/FGP failure modes Codex measured as most damaging. Accounting: Classes 1-3 (identity) and Class 6 (catalogue divergence) are KEPT UNCHANGED (Class 6 carries substantive owner rulings F/G on specific real cases -- dropping it would discard that work). Class 4 (terse/missing catalogue text) and Class 7 (liturgical-container predictability) are FOLDED IN as strata of the new Arm 1 (residual), per the owner's own instruction. Class 5 (generic collection works) is DROPPED: no owner ruling exists for any specific Class 5 case, and its collection-level-identity question does not correspond to a source-coverage stratum.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>IMPORTANT: a BLANK verdict cell (Identity, Shade, or Demotion) is NOT a label -- it means "not yet answered". If you cannot judge a case, enter `unsure` explicitly (it costs nothing and is a real, useful answer) rather than leaving the cell blank. If you choose not to judge a case at all, enter `skip` explicitly -- it is recorded as skipped, never silently filled from the case's own draft PROPOSAL. The Correctness column (Novelty Shades sheet) is meaningful ONLY when the Shade verdict is `diverges_work` or `diverges_part` -- leave it blank on every other row. The No-Source-Text sheet has NO verdict column at all -- these rows ship as candidates automatically regardless of what you observe there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Identity answer</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Choose this when...</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>same_work</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>A and B are the same underlying work (or two parts/granularities of the same work)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>different_works</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>A and B are genuinely different works</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>unsure</t>
+          <t>same_work</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>you cannot judge this pair from the information shown -- a real and useful answer</t>
+          <t>A and B are the same underlying work (or two parts/granularities of the same work)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>different_works</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>A and B are genuinely different works</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>unsure</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>you cannot judge this pair from the information shown -- a real and useful answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>you choose not to judge this pair at all -- recorded as skipped</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Shade</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Choose this when...</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>confirms</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>an aid already ties this fragment to this work</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>refines_granularity</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>OUR claim is MORE SPECIFIC (finer) than what an aid says -- e.g. the catalogue names the whole work, our claim names a specific book/chapter of it (the D-13d same-author/related-title rule); the OPPOSITE direction from `aid_more_specific` -- we ADD precision here. OWNER RULING G: if the aid's own FREE TEXT already states this identification in ANY form (even under a coarser structured work-id), the correct shade is `confirms`, not this one -- reserve `refines_granularity` for information the aid contains in NO form, structured or free.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>aid_more_specific</t>
+          <t>confirms</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>an AID names a MORE SPECIFIC (finer) variant of this fragment's work than our claim does -- e.g. the catalogue names a chapter/book, our claim names the whole work (the D-13d same-author/related-title rule); the OPPOSITE direction from `refines_granularity` -- we add NOTHING here, the aid already knew more (owner correction E′; the LEAST novel shade)</t>
+          <t>an aid already ties this fragment to this work</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>diverges_work</t>
+          <t>refines_granularity</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>an aid ties this fragment to a genuinely DIFFERENT WORK (not a granularity variant of ours) -- the aid and the claim contradict each other on WHICH WORK this is (owner ruling F, replacing the single `diverges` token). Owner: reading real cases, USUALLY the catalogue is right and this is OUR false positive -- but not always; record which side is correct in the separate Correctness column. Hidden by default on every surface, behind an explicit warned toggle -- never silently shown, never silently suppressed.</t>
+          <t>OUR claim is MORE SPECIFIC (finer) than what an aid says -- e.g. the catalogue names the whole work, our claim names a specific book/chapter of it (the D-13d same-author/related-title rule); the OPPOSITE direction from `aid_more_specific` -- we ADD precision here. OWNER RULING G: if the aid's own FREE TEXT already states this identification in ANY form (even under a coarser structured work-id), the correct shade is `confirms`, not this one -- reserve `refines_granularity` for information the aid contains in NO form, structured or free.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>diverges_part</t>
+          <t>aid_more_specific</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>an aid ties this fragment to a DIFFERENT OR FINER PART of the SAME work (owner ruling F -- "more delicate and essentially less important" than diverges_work) -- e.g. the aid names a specific chapter/section of the work while we name a different one, or the whole work, or vice versa. Same Correctness column and same hidden-by-default posture as diverges_work.</t>
+          <t>an AID names a MORE SPECIFIC (finer) variant of this fragment's work than our claim does -- e.g. the catalogue names a chapter/book, our claim names the whole work (the D-13d same-author/related-title rule); the OPPOSITE direction from `refines_granularity` -- we add NOTHING here, the aid already knew more (owner correction E′; the LEAST novel shade)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>container_predicts</t>
+          <t>diverges_work</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>an aid names a BROADER rite/cycle/ceremony/container -- a full standard-rite prayer-book (siddur/machzor) or a named ceremony/occasion -- whose STANDARD, PREDICTABLE content includes this specific unit, WITHOUT ever naming the unit itself (owner ruling H; e.g. the catalogue names 'מחזור מנהג אשכנז לשלש רגלים', the claim is a Yotzer for one of its festivals). Distinct from `confirms` (the aid never names this specific unit) and from `fills_gap` (the content IS predictable, so it is not 'previously unknown' -- under the pre-H enum this fell through to `fills_gap` by elimination). Excluded from the candidate toggle like every other non-`fills_gap` shade, but -- UNLIKE `diverges_work`/`diverges_part` -- shown NORMALLY, never hidden by default: there is no disagreement here to warn about, only a container relationship.</t>
+          <t>an aid ties this fragment to a genuinely DIFFERENT WORK (not a granularity variant of ours) -- the aid and the claim contradict each other on WHICH WORK this is (owner ruling F, replacing the single `diverges` token). Owner: reading real cases, USUALLY the catalogue is right and this is OUR false positive -- but not always; record which side is correct in the separate Correctness column. Hidden by default on every surface, behind an explicit warned toggle -- never silently shown, never silently suppressed.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>fills_gap</t>
+          <t>diverges_part</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>the aids identify this fragment as nothing at all -- the genuine "previously unknown" case</t>
+          <t>an aid ties this fragment to a DIFFERENT OR FINER PART of the SAME work (owner ruling F -- "more delicate and essentially less important" than diverges_work) -- e.g. the aid names a specific chapter/section of the work while we name a different one, or the whole work, or vice versa. Same Correctness column and same hidden-by-default posture as diverges_work.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>extends</t>
+          <t>container_predicts</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>aids tie OTHER folios of the SAME manuscript to this work, but not this specific folio</t>
+          <t>an aid names a BROADER rite/cycle/ceremony/container -- a full standard-rite prayer-book (siddur/machzor) or a named ceremony/occasion -- whose STANDARD, PREDICTABLE content includes this specific unit, WITHOUT ever naming the unit itself (owner ruling H; e.g. the catalogue names 'מחזור מנהג אשכנז לשלש רגלים', the claim is a Yotzer for one of its festivals). Distinct from `confirms` (the aid never names this specific unit) and from `fills_gap` (the content IS predictable, so it is not 'previously unknown' -- under the pre-H enum this fell through to `fills_gap` by elimination). Excluded from the candidate toggle like every other non-`fills_gap` shade, but -- UNLIKE `diverges_work`/`diverges_part` -- shown NORMALLY, never hidden by default: there is no disagreement here to warn about, only a container relationship.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>alias_merge</t>
+          <t>fills_gap</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>the two work_ids shown ARE the same underlying work, not yet canonically merged (Class 2's situation)</t>
+          <t>the aids identify this fragment as nothing at all -- the genuine "previously unknown" case</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>unsure</t>
+          <t>extends</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>you cannot judge this case from the information shown -- maps to `not_checked`, costs nothing, is a real and useful answer</t>
+          <t>aids tie OTHER folios of the SAME manuscript to this work, but not this specific folio</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>alias_merge</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>you choose not to judge this case at all -- recorded as skipped, NEVER filled from a draft `PROPOSAL`</t>
+          <t>the two work_ids shown ARE the same underlying work, not yet canonically merged (Class 2's situation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>unsure</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>you cannot judge this case from the information shown -- maps to `not_checked`, costs nothing, is a real and useful answer</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>you choose not to judge this case at all -- recorded as skipped, NEVER filled from a draft `PROPOSAL`</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>`not_checked` (the fail-closed system default for an unrun/failed/abstained check) is not a verdict you pick directly -- `unsure` is its owner-facing equivalent.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Correctness (divergence rows only)</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Correctness (Class 6 divergence rows only)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Choose this when...</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>catalogue_correct</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>the catalogue/aid is right; our claim is the false positive -- owner ruling F: reading the real cases, this is the COMMON outcome</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>claim_correct</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>our claim is right; the aid is wrong, thinner, or itself mistaken</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>catalogue_correct</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>the catalogue/aid is right; our claim is the false positive -- owner ruling F: reading the real cases, this is the COMMON outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>claim_correct</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>our claim is right; the aid is wrong, thinner, or itself mistaken</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t>unclear</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>cannot tell which side is correct from the information shown</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Plausible answers (a reading aid -- any answer above is still valid)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Class 3 -- catalogue entry naming a different granularity of the same work (IDENTITY spot-check)</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>same_work, different_works</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Class 2 -- alias pairs (IDENTITY spot-check)</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>same_work, different_works</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Demotion verdict (Heuristic-Demoted sheet)</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Choose this when...</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Class 1 -- near-miss titles (IDENTITY spot-check)</t>
+          <t>demotion_correct</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>same_work, different_works</t>
+          <t>the demoting source genuinely already names/records THIS SPECIFIC work on THIS fragment -- the heuristic's demotion (marking it already known, never reaching the model) is right</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Class 4 -- terse or missing catalogue identification text (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>false_known</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms</t>
+          <t>the demoting source does NOT actually name this specific work -- only its GENERIC presence (e.g. a bibliography record, a PGP description/transcription on the fragment) tripped the heuristic. Per owner ruling J this is an UNRECOVERABLE lost finding: the funnel only ever demotes (discovery -&gt; known, never the reverse) and the model never sees a heuristically-demoted row, so a false_known here is permanent unless this labelling catches it</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Class 5 -- generic collection works (NOVELTY SHADE, owner-authorized extension)</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>fills_gap, confirms, extends</t>
+          <t>you cannot judge this case from the information shown -- a real and useful answer</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G)</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
+          <t>you choose not to judge this case at all -- recorded as skipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Class / Arm</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Plausible answers (a reading aid -- any answer above is still valid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Class 3 -- catalogue entry naming a different granularity of the same work (IDENTITY spot-check)</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>same_work, different_works</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Class 2 -- alias pairs (IDENTITY spot-check)</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>same_work, different_works</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Class 1 -- near-miss titles (IDENTITY spot-check)</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>same_work, different_works</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Class 6 -- catalogue divergence (NOVELTY SHADE, owner rulings E/E′/F/G -- RETAINED UNCHANGED by the ruling-J redesign)</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
           <t>diverges_work, diverges_part, aid_more_specific, refines_granularity, confirms</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Class 7 -- liturgical-container predictability (NOVELTY SHADE, owner rulings H/I)</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>container_predicts, fills_gap, confirms</t>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Arm 1 -- RESIDUAL: rows that would reach the model (NOVELTY SHADE, source-stratified, owner ruling J -- folds in the former Classes 4 and 7)</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>fills_gap, confirms, container_predicts, refines_granularity, aid_more_specific</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Arm 2 -- HEURISTIC-DEMOTED: rows the funnel marks known before any model call (DEMOTION CORRECTNESS, owner ruling J)</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>demotion_correct, false_known, unsure, skip</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Arm 3 -- NO-SOURCE-TEXT: rows shipped as candidates with no verdict (owner ruling J)</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>(no verdict collected -- informational only)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A26:B26"/>
+  <mergeCells count="5">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
